--- a/artifacts/uat/UAT_LOGISTIK_END_TO_END_TESTER.xlsx
+++ b/artifacts/uat/UAT_LOGISTIK_END_TO_END_TESTER.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Akun Tester" sheetId="1" r:id="R6c10dea0bb5f4c5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Checklist UAT" sheetId="2" r:id="Rb502b9a047a145f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Ringkasan" sheetId="3" r:id="R57636c812bb241cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Akun Tester" sheetId="1" r:id="R213c0d2399d945f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Checklist UAT" sheetId="2" r:id="R997cccf13ae4449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Ringkasan" sheetId="3" r:id="R0d630e9cfab5463a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -487,10 +487,33 @@
         <x:v>Jika akun tidak ada setelah reset, buat dari Supir -&gt; Akses Mobile.</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="64.5" customHeight="1">
+      <x:c r="A10" s="2" t="str">
+        <x:v>Portal Driver / Mobile Driver</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="str">
+        <x:v>DRIVER - Imam</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="str">
+        <x:v>imam@driver</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="str">
+        <x:v>driver12345</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="str">
+        <x:v>/driver/login dan app mobile</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="str">
+        <x:v>UAT case Imam: trip baru setelah DO lama selesai, input SJ/barang dari mobile.</x:v>
+      </x:c>
+      <x:c r="G10" s="2" t="str">
+        <x:v>Password sudah di-reset untuk UAT pada 2026-05-13.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra03d467bee46417a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R154e98fb6dfd49c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5321,7 +5344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61b80bd85fc3435f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a0701773c0847f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5443,7 +5466,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f1557ac2f884123"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R872912361fb745b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/artifacts/uat/UAT_LOGISTIK_END_TO_END_TESTER.xlsx
+++ b/artifacts/uat/UAT_LOGISTIK_END_TO_END_TESTER.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Akun Tester" sheetId="1" r:id="R213c0d2399d945f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Checklist UAT" sheetId="2" r:id="R997cccf13ae4449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Ringkasan" sheetId="3" r:id="R0d630e9cfab5463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Akun Tester" sheetId="1" r:id="R3e835a1a924e4fd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Checklist UAT" sheetId="2" r:id="R8db09057ec9f4330"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Ringkasan" sheetId="3" r:id="Rb237ebe0d27e427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Mobile Admin Detail" sheetId="4" r:id="R15158453f2b7438d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -117,6 +118,28 @@
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Metric"/>
     <x:tableColumn id="2" name="Value"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table1" displayName="Table1" ref="A1:N39" headerRowCount="1">
+  <x:tableColumns count="14">
+    <x:tableColumn id="1" name="ID"/>
+    <x:tableColumn id="2" name="Modul"/>
+    <x:tableColumn id="3" name="Submodul"/>
+    <x:tableColumn id="4" name="Prioritas"/>
+    <x:tableColumn id="5" name="Login yang Dipakai"/>
+    <x:tableColumn id="6" name="Masuk Dari / Menu"/>
+    <x:tableColumn id="7" name="Data Uji"/>
+    <x:tableColumn id="8" name="Cara Test Detail"/>
+    <x:tableColumn id="9" name="Output yang Diharapkan"/>
+    <x:tableColumn id="10" name="Hasil"/>
+    <x:tableColumn id="11" name="Bug / Ketidaksesuaian"/>
+    <x:tableColumn id="12" name="Evidence"/>
+    <x:tableColumn id="13" name="Tester"/>
+    <x:tableColumn id="14" name="Tanggal"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -513,7 +536,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R154e98fb6dfd49c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3d3438e87bb4e00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -676,16 +699,10 @@
         <x:v>Validasi driver bisa tambah/edit/hapus SJ sebelum aktual final tanpa merusak admin.</x:v>
       </x:c>
       <x:c r="G4" s="2" t="str">
-        <x:v>1. Assign trip
-2. driver input SJ
-3. edit nomor salah
-4. tambah SJ tambahan
-5. hapus SJ salah
-6. tambah/edit barang
-7. admin review.</x:v>
+        <x:v>Lihat sheet 03 Mobile Admin Detail: MOBADM-003 sampai MOBADM-006. Jalankan dari Mobile Kelola SJ &amp; Barang, lalu cek Web Admin /surat-jalan dan /delivery-orders/{id}.</x:v>
       </x:c>
       <x:c r="H4" s="2" t="str">
-        <x:v>Admin melihat data SJ/barang final benar; tidak ada stale SJ/item.</x:v>
+        <x:v>SJ dan barang tampil per card/SJ, master barang stabil, edit/hapus memakai warning, dan admin membaca data final tanpa stale/duplikat.</x:v>
       </x:c>
       <x:c r="I4" s="2" t="str">
         <x:v>Belum Dites</x:v>
@@ -715,12 +732,10 @@
         <x:v>Pastikan final fatal tetap approval admin.</x:v>
       </x:c>
       <x:c r="G5" s="2" t="str">
-        <x:v>1. Driver ajukan selesai dengan actual/drop/POD
-2. admin approve atau reject
-3. driver koreksi bila reject.</x:v>
+        <x:v>Lihat sheet 03 Mobile Admin Detail: MOBADM-011 sampai MOBADM-017. Jalankan Mobile Ajukan Selesai, lalu approve/reject dari Web Admin /delivery-orders/{id}.</x:v>
       </x:c>
       <x:c r="H5" s="2" t="str">
-        <x:v>DO hanya DELIVERED setelah approve admin; pending lock aktif selama menunggu.</x:v>
+        <x:v>Aktual barang, titik drop, hold, dan approval admin sinkron. DO hanya Delivered setelah admin approve final.</x:v>
       </x:c>
       <x:c r="I5" s="2" t="str">
         <x:v>Belum Dites</x:v>
@@ -750,13 +765,10 @@
         <x:v>Validasi insiden lapangan dan biaya.</x:v>
       </x:c>
       <x:c r="G6" s="2" t="str">
-        <x:v>1. Driver lapor insiden
-2. admin armada review
-3. driver/admin input resolution cost
-4. finance posting/expense bila disetujui.</x:v>
+        <x:v>Lihat sheet 03 Mobile Admin Detail: MOBADM-020 sampai MOBADM-026. Jalankan Mobile Lapor Insiden/Ajukan Selesai Insiden, lalu review di Admin /fleet/incidents/{id} dan /driver-vouchers/{id}.</x:v>
       </x:c>
       <x:c r="H6" s="2" t="str">
-        <x:v>Incident resolved/closed dan biaya tercatat tanpa dobel posting.</x:v>
+        <x:v>Insiden aktif mengunci laporan baru, pengajuan selesai terlihat di admin, biaya approved masuk uang jalan/biaya lain-lain tanpa pending stale atau double posting.</x:v>
       </x:c>
       <x:c r="I6" s="2" t="str">
         <x:v>Belum Dites</x:v>
@@ -786,15 +798,10 @@
         <x:v>Validasi kas uang jalan dan settlement trip.</x:v>
       </x:c>
       <x:c r="G7" s="2" t="str">
-        <x:v>1. DO aktif
-2. terbit uang jalan
-3. top up
-4. biaya trip
-5. settle sisa/kekurangan
-6. laporan kas.</x:v>
+        <x:v>Lihat sheet 03 Mobile Admin Detail: MOBADM-024, MOBADM-025, dan ADM-003. Cek kasus voucher sudah terbit dan belum terbit.</x:v>
       </x:c>
       <x:c r="H7" s="2" t="str">
-        <x:v>Voucher SETTLED, expense dan bankTransaction benar, tidak bisa dobel borongan.</x:v>
+        <x:v>Biaya trip dan biaya insiden tertaut ke uang jalan trip yang benar, termasuk kasus approve insiden sebelum bon diterbitkan.</x:v>
       </x:c>
       <x:c r="I7" s="2" t="str">
         <x:v>Belum Dites</x:v>
@@ -5344,7 +5351,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a0701773c0847f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R615accf5465b4b10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5370,8 +5377,8 @@
         <x:v>Total Checklist</x:v>
       </x:c>
       <x:c r="B2" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!A:A,"&lt;&gt;")-1</x:f>
-        <x:v>131</x:v>
+        <x:f>COUNTA('01 Checklist UAT'!A2:A500)+COUNTA('03 Mobile Admin Detail'!A2:A500)</x:f>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="40.5" customHeight="1">
@@ -5379,8 +5386,8 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="B3" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!D:D,"P0")</x:f>
-        <x:v>93</x:v>
+        <x:f>COUNTIF('01 Checklist UAT'!D:D,"P0")+COUNTIF('03 Mobile Admin Detail'!D:D,"P0")</x:f>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="40.5" customHeight="1">
@@ -5388,8 +5395,8 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="B4" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!D:D,"P1")</x:f>
-        <x:v>36</x:v>
+        <x:f>COUNTIF('01 Checklist UAT'!D:D,"P1")+COUNTIF('03 Mobile Admin Detail'!D:D,"P1")</x:f>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="40.5" customHeight="1">
@@ -5397,7 +5404,7 @@
         <x:v>P2</x:v>
       </x:c>
       <x:c r="B5" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!D:D,"P2")</x:f>
+        <x:f>COUNTIF('01 Checklist UAT'!D:D,"P2")+COUNTIF('03 Mobile Admin Detail'!D:D,"P2")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -5406,7 +5413,7 @@
         <x:v>Sesuai</x:v>
       </x:c>
       <x:c r="B6" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!I:I,"Sesuai")</x:f>
+        <x:f>COUNTIF('01 Checklist UAT'!I:I,"Sesuai")+COUNTIF('03 Mobile Admin Detail'!J:J,"Sesuai")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -5415,7 +5422,7 @@
         <x:v>Ada Bug</x:v>
       </x:c>
       <x:c r="B7" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!I:I,"Ada Bug")</x:f>
+        <x:f>COUNTIF('01 Checklist UAT'!I:I,"Ada Bug")+COUNTIF('03 Mobile Admin Detail'!J:J,"Ada Bug")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -5424,7 +5431,7 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="B8" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!I:I,"Blocked")</x:f>
+        <x:f>COUNTIF('01 Checklist UAT'!I:I,"Blocked")+COUNTIF('03 Mobile Admin Detail'!J:J,"Blocked")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -5433,7 +5440,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="B9" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!I:I,"N/A")</x:f>
+        <x:f>COUNTIF('01 Checklist UAT'!I:I,"N/A")+COUNTIF('03 Mobile Admin Detail'!J:J,"N/A")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -5442,8 +5449,8 @@
         <x:v>Belum Dites</x:v>
       </x:c>
       <x:c r="B10" s="2" t="n">
-        <x:f>COUNTIF('01 Checklist UAT'!I:I,"Belum Dites")</x:f>
-        <x:v>131</x:v>
+        <x:f>COUNTIF('01 Checklist UAT'!I:I,"Belum Dites")+COUNTIF('03 Mobile Admin Detail'!J:J,"Belum Dites")</x:f>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="40.5" customHeight="1">
@@ -5451,22 +5458,1470 @@
         <x:v>Pass Rate</x:v>
       </x:c>
       <x:c r="B11" s="6" t="n">
-        <x:f>IF(B2=0,"",B6/B2)</x:f>
+        <x:f>IF(B2=0,0,B6/B2)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="40.5" customHeight="1">
       <x:c r="A12" s="2" t="str">
+        <x:v>Detail Mobile/Admin</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="str">
+        <x:v>38 checklist di sheet 03 Mobile Admin Detail</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
         <x:v>Catatan</x:v>
       </x:c>
-      <x:c r="B12" s="2" t="str">
-        <x:v>Isi detail bug langsung di sheet 01 Checklist UAT pada kolom Bug / Ketidaksesuaian.</x:v>
+      <x:c r="B13" t="str">
+        <x:v>Isi detail bug di kolom Bug / Ketidaksesuaian dan lampirkan evidence screenshot/log.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R872912361fb745b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R271be970fbb74c1f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11.569999694824219" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.31999969482422" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48.18000030517578" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="63.38999938964844" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="97.16999816894531" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="74.83000183105469" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="141.99000549316406" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="174.2899932861328" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20.729999542236328" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="9.829999923706055" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="7.539999961853027" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="8.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Modul</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>Submodul</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>Prioritas</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>Login yang Dipakai</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>Masuk Dari / Menu</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>Data Uji</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>Cara Test Detail</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>Output yang Diharapkan</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>Hasil</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>Bug / Ketidaksesuaian</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>Tester</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>Tanggal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>MOBADM-001</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>Akses &amp; Isolasi Data</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>Login driver hanya melihat trip miliknya</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>Mobile Driver: driver.eko@company.local / driver12345, lalu driver lain bila ada</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>APK Mobile -&gt; Login Driver -&gt; Beranda</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>Minimal 2 driver dan 2 trip berbeda.</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>Login sebagai Driver A, catat daftar trip. Logout, login Driver B, catat daftar trip. Bandingkan dengan Web Admin /delivery-orders.</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>Driver hanya melihat trip yang ditugaskan ke dirinya. Trip driver lain tidak muncul, tidak bisa dibuka, dan tidak bisa diupdate lewat API mobile.</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K2" t="str"/>
+      <x:c r="L2" t="str"/>
+      <x:c r="M2" t="str"/>
+      <x:c r="N2" t="str"/>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>MOBADM-002</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Assign Admin</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>Driver/truk aktif terkunci sebelum trip selesai</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>Web Admin OPERASIONAL: admin@company.local / admin12345</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Web Admin /login -&gt; Kerja Harian -&gt; Trip / Delivery Order (/delivery-orders) -&gt; Detail trip -&gt; Lengkapi Armada Trip</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>1 driver, 1 truk, 2 order/trip baru.</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>Assign driver dan truk ke Trip A yang belum selesai. Buka Trip B dan coba assign driver/truk yang sama. Setelah Trip A selesai/final, ulangi assign ke Trip B.</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>Saat Trip A belum selesai, driver/truk tidak tersedia atau diberi status sibuk. Setelah Trip A delivered/final/closed, driver dan truk bisa dipakai lagi tanpa data lama ikut berubah.</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K3" t="str"/>
+      <x:c r="L3" t="str"/>
+      <x:c r="M3" t="str"/>
+      <x:c r="N3" t="str"/>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" t="str">
+        <x:v>MOBADM-003</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Manifest Mobile</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>Tambah SJ pertama dan barang dari master</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>APK Mobile -&gt; Beranda -&gt; Pilih trip -&gt; Kelola SJ &amp; Barang</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>Trip baru status Dibuat/Menuju Pickup dengan customer yang punya master barang.</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>Tekan Kelola SJ &amp; Barang. Isi No SJ pengirim. Tekan Tambah Barang di SJ Ini. Buka dropdown Pilih master barang, cari barang, pilih barang, isi koli/berat/volume sesuai pola admin.</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>Dropdown tetap terbuka saat keyboard muncul. Setelah pilih master, nama barang/satuan/dimensi dasar terisi sesuai master. Input angka menerima format yang sama seperti admin dan tidak membuat halaman hilang.</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K4" t="str"/>
+      <x:c r="L4" t="str"/>
+      <x:c r="M4" t="str"/>
+      <x:c r="N4" t="str"/>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" t="str">
+        <x:v>MOBADM-004</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Manifest Mobile</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Tambah SJ kedua tidak merusak SJ pertama</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>Mobile Kelola SJ &amp; Barang, lalu Web Admin /surat-jalan dan /delivery-orders/{id}</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>Trip dengan SJ A sudah disimpan dan punya barang.</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>Di mobile tambah SJ B dan barang baru. Simpan. Refresh mobile dan buka admin Surat Jalan.</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>SJ A tetap ada dengan barang dan status yang sama. SJ B muncul sebagai SJ baru. Tidak ada barang SJ A berpindah ke SJ B, tidak ada duplikasi, dan total barang admin sama dengan mobile.</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K5" t="str"/>
+      <x:c r="L5" t="str"/>
+      <x:c r="M5" t="str"/>
+      <x:c r="N5" t="str"/>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>MOBADM-005</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Manifest Mobile</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Edit SJ dan edit barang sebelum final</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>Mobile Kelola SJ &amp; Barang -&gt; Card per SJ -&gt; edit nomor/barang</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>Trip belum final, punya minimal 2 SJ dan beberapa barang.</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>Edit nomor SJ, edit deskripsi barang, koli, berat, volume, satuan, dan catatan. Simpan lalu cek admin /surat-jalan.</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>Data yang diedit muncul di admin sesuai nilai terakhir. Field yang lock di admin ikut lock di mobile. Field yang boleh beda di admin tetap bisa diedit di mobile sebelum final.</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K6" t="str"/>
+      <x:c r="L6" t="str"/>
+      <x:c r="M6" t="str"/>
+      <x:c r="N6" t="str"/>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>MOBADM-006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Manifest Mobile</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Hapus SJ dan barang memakai istilah Hapus/Tolak</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Mobile Kelola SJ &amp; Barang -&gt; tombol Hapus pada card SJ/barang</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Trip belum final, punya draft SJ tambahan dan barang tambahan.</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Hapus barang draft, hapus SJ draft, lalu hapus SJ/barang yang sudah tersimpan. Cek dialog konfirmasi.</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>UI memakai istilah Hapus atau Tolak, bukan Void. Ada warning sebelum hapus. Data belum dikirim sebelum Simpan. Setelah Simpan, admin tidak melihat stale item yang harusnya terhapus.</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K7" t="str"/>
+      <x:c r="L7" t="str"/>
+      <x:c r="M7" t="str"/>
+      <x:c r="N7" t="str"/>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>MOBADM-007</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Status SJ Batch</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Update satu SJ tidak mengubah SJ lain</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Mobile -&gt; Trip -&gt; Update Status SJ, Admin -&gt; /surat-jalan atau /delivery-orders/{id}</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>Trip punya SJ A dan SJ B sama-sama status Dibuat.</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>Buka Update Status SJ. Pilih status Menuju Pickup. Centang hanya SJ A. Submit. Refresh mobile dan admin.</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>SJ A berubah ke Menuju Pickup. SJ B tetap Dibuat. Status trip utama hanya mengikuti agregasi progres, bukan mereset semua SJ.</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K8" t="str"/>
+      <x:c r="L8" t="str"/>
+      <x:c r="M8" t="str"/>
+      <x:c r="N8" t="str"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>MOBADM-008</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Status SJ Batch</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>SJ progressed tidak reset saat tambah SJ baru</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>Mobile -&gt; Update Status SJ, lalu Kelola SJ &amp; Barang</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>Trip punya SJ A.</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>Update SJ A sampai Arrived atau Dalam Pengiriman. Setelah itu tambah SJ B lewat Kelola SJ &amp; Barang. Simpan dan refresh.</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>SJ A tetap pada status terakhirnya. SJ B mulai dari Dibuat. Tidak ada status SJ yang balik ke Pickup/Dibuat karena ada SJ baru.</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K9" t="str"/>
+      <x:c r="L9" t="str"/>
+      <x:c r="M9" t="str"/>
+      <x:c r="N9" t="str"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>MOBADM-009</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Status SJ Batch</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Pilihan status sama konsep admin operasional</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>Admin /delivery-orders/{id} atau /surat-jalan/{id} -&gt; Ubah Status, Mobile -&gt; Update Status SJ</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>Trip dengan SJ di beberapa status: Dibuat, Menuju Pickup, Pickup, Dalam Pengiriman, Arrived.</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>Bandingkan pilihan status lanjutan di admin dan di mobile untuk setiap status awal. Coba status yang tidak boleh lompat.</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>Mobile hanya menawarkan status transisi yang valid seperti admin. Tidak ada pilihan yang membuat workflow loncat approval/final.</x:v>
+      </x:c>
+      <x:c r="J10" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K10" t="str"/>
+      <x:c r="L10" t="str"/>
+      <x:c r="M10" t="str"/>
+      <x:c r="N10" t="str"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>MOBADM-010</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Status SJ Batch</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Tidak bisa submit tanpa memilih SJ</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>Mobile -&gt; Update Status SJ</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>Trip punya minimal 2 SJ yang bisa diupdate.</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>Buka modal Update Status SJ. Hilangkan semua centang. Coba submit.</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>Tombol update disabled atau menampilkan warning jelas. Tidak ada request kosong yang mengubah status trip atau SJ.</x:v>
+      </x:c>
+      <x:c r="J11" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K11" t="str"/>
+      <x:c r="L11" t="str"/>
+      <x:c r="M11" t="str"/>
+      <x:c r="N11" t="str"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>MOBADM-011</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Finalisasi Drop</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Aktual barang per SJ dan per item</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>Mobile -&gt; Ajukan Selesai -&gt; Aktual Barang, Admin -&gt; /delivery-orders/{id} tab aktual</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>Trip punya 2 SJ dengan barang berbeda.</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Ajukan selesai. Isi aktual koli/berat/volume untuk barang SJ A dan SJ B secara terpisah. Simpan, lalu cek admin.</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>Aktual tiap barang tetap menempel pada SJ yang benar. Tidak ada barang campur antar SJ. Admin menampilkan angka aktual sama dengan mobile.</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K12" t="str"/>
+      <x:c r="L12" t="str"/>
+      <x:c r="M12" t="str"/>
+      <x:c r="N12" t="str"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>MOBADM-012</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Finalisasi Drop</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Qty order dan aktual boleh berbeda sesuai admin</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>Mobile -&gt; Ajukan Selesai -&gt; Aktual Barang, Admin -&gt; /delivery-orders/{id}</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>Barang target qty/koli 10 atau berat tertentu.</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>Isi aktual lebih kecil dari target untuk partial, lalu ajukan. Ulangi dengan aktual berbeda pada berat/volume bila workflow admin memperbolehkan.</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>Mobile mengikuti aturan admin: qty/koli/berat aktual bisa beda dari order bila admin juga memperbolehkan. Sistem tidak memaksa angka sama kecuali field memang wajib/terkunci.</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K13" t="str"/>
+      <x:c r="L13" t="str"/>
+      <x:c r="M13" t="str"/>
+      <x:c r="N13" t="str"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>MOBADM-013</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Finalisasi Drop</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>Satu titik drop otomatis untuk semua barang</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>Mobile -&gt; Ajukan Selesai -&gt; Titik Drop, Admin -&gt; /delivery-orders/{id} -&gt; Realisasi Drop</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>Trip semua barang selesai di satu tujuan invoice.</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Pada langkah titik drop, gunakan default Tujuan Invoice/Semua manual. Jangan buat split per item. Ajukan lalu cek admin.</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>Sistem otomatis mengalokasikan semua barang ke satu titik drop. Total aktual drop = total aktual barang. Invoice mengambil barang billable yang benar.</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K14" t="str"/>
+      <x:c r="L14" t="str"/>
+      <x:c r="M14" t="str"/>
+      <x:c r="N14" t="str"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>MOBADM-014</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Finalisasi Drop</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Multi drop beda tempat per barang</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>Mobile -&gt; Ajukan Selesai -&gt; Tambah Titik Drop, Admin -&gt; /delivery-orders/{id} dan /surat-jalan/{id}</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>Trip punya minimal 2 barang/SJ dengan tujuan beda.</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Buat Drop 1 untuk barang SJ A, Drop 2 untuk barang SJ B. Pilih barang spesifik per titik. Isi lokasi/catatan. Ajukan dan cek admin.</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>Drop tidak tercampur. Tiap titik menampilkan barang yang dipilih. Jika ada campuran drop dan hold, mobile meminta pilih barang spesifik sebelum finalisasi.</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K15" t="str"/>
+      <x:c r="L15" t="str"/>
+      <x:c r="M15" t="str"/>
+      <x:c r="N15" t="str"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>MOBADM-015</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Hold / Lanjutan</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Sebagian barang hold tetap bisa dilanjutkan</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>Mobile -&gt; Ajukan Selesai -&gt; Titik Drop tipe Hold / Inap, Admin -&gt; /delivery-orders dan /surat-jalan</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>Trip punya 2 barang, satu drop dan satu hold.</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Finalisasi dengan barang A drop, barang B Hold/Inap. Admin approve. Lanjutkan dari barang hold melalui flow lanjutan admin/mobile sesuai ketersediaan.</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>Barang drop masuk billable. Barang hold tidak hilang dan bisa dilanjutkan. Tidak ada qty negatif atau double bill di invoice.</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K16" t="str"/>
+      <x:c r="L16" t="str"/>
+      <x:c r="M16" t="str"/>
+      <x:c r="N16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>MOBADM-016</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Approval Admin</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Driver ajukan selesai membuat pending approval</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>Mobile -&gt; Ajukan Selesai, Admin -&gt; /delivery-orders/{id}</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>Trip siap finalisasi.</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Driver ajukan selesai. Sebelum approve, refresh mobile dan admin.</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>Admin melihat status pending driver approval. Mobile menampilkan menunggu approval admin dan mengunci update final yang tidak boleh diedit. DO belum Delivered sebelum admin approve.</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K17" t="str"/>
+      <x:c r="L17" t="str"/>
+      <x:c r="M17" t="str"/>
+      <x:c r="N17" t="str"/>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>MOBADM-017</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Approval Admin</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Admin reject, driver koreksi dan ajukan lagi</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>Admin /delivery-orders/{id} -&gt; Tolak/Kembalikan, Mobile -&gt; Ajukan Selesai</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>Ada request finalisasi driver pending.</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>Admin tolak dengan catatan. Driver buka mobile, baca catatan, edit aktual/drop, ajukan ulang. Admin approve.</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>Catatan reject tampil di mobile. Setelah koreksi, request lama tidak menggantung. Approval baru menghasilkan data final yang benar.</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K18" t="str"/>
+      <x:c r="L18" t="str"/>
+      <x:c r="M18" t="str"/>
+      <x:c r="N18" t="str"/>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" t="str">
+        <x:v>MOBADM-018</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>Odometer</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Input odometer tutup trip valid</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL/ARMADA</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>Mobile -&gt; Trip delivered -&gt; Tutup Trip, Admin -&gt; kendaraan/trip detail</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>Trip delivered dengan kendaraan punya odometer terakhir.</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>Tekan Tutup Trip. Isi odometer akhir lebih besar dari odometer kendaraan terakhir. Submit dan cek admin.</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>Trip closure request tercatat. Setelah admin approve/close, odometer kendaraan ikut nilai akhir. Format angka sesuai admin dan tidak menerima nilai kosong.</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K19" t="str"/>
+      <x:c r="L19" t="str"/>
+      <x:c r="M19" t="str"/>
+      <x:c r="N19" t="str"/>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>MOBADM-019</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Odometer</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Odometer lebih kecil ditolak</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>Mobile -&gt; Tutup Trip atau Lapor Insiden -&gt; field odometer</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>Trip dengan vehicleLastOdometer terisi.</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>Isi odometer lebih kecil dari odometer kendaraan terakhir, lalu submit.</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>Mobile menolak sebelum kirim atau backend menolak dengan pesan jelas. Tidak ada trip closure/incident resolution tersimpan dengan odometer mundur.</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K20" t="str"/>
+      <x:c r="L20" t="str"/>
+      <x:c r="M20" t="str"/>
+      <x:c r="N20" t="str"/>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>MOBADM-020</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Insiden Mobile</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Lapor insiden pertama dari driver</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Mobile Driver + Web Admin ARMADA</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Mobile -&gt; Trip -&gt; Lapor Insiden, Admin -&gt; Armada -&gt; Insiden (/fleet/incidents)</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>Trip aktif dengan driver login.</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>Driver buka Lapor Insiden, pilih tipe/severity, isi lokasi/odometer/catatan, kirim. Admin buka daftar insiden.</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>Insiden muncul di admin dengan nomor INC, trip/driver/kendaraan tertaut, status awal Dalam Proses/Ditangani sesuai workflow, dan lokasi masuk.</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K21" t="str"/>
+      <x:c r="L21" t="str"/>
+      <x:c r="M21" t="str"/>
+      <x:c r="N21" t="str"/>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>MOBADM-021</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Insiden Mobile</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Saat ada insiden aktif, Lapor Insiden disembunyikan</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Mobile -&gt; Trip yang punya active incident</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>Trip punya 1 insiden belum CLOSED.</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>Refresh mobile setelah insiden dibuat. Lihat area insiden.</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>UI tidak menampilkan tombol Lapor Insiden lagi. Yang tampil hanya aksi relevan seperti Ajukan Selesai Insiden atau status menunggu admin. Tidak ada duplikasi laporan aktif.</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K22" t="str"/>
+      <x:c r="L22" t="str"/>
+      <x:c r="M22" t="str"/>
+      <x:c r="N22" t="str"/>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>MOBADM-022</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Insiden Mobile</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Driver ajukan selesai insiden dengan biaya</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Mobile Driver + Web Admin ARMADA</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>Mobile -&gt; Ajukan Selesai Insiden, Admin -&gt; /fleet/incidents/{id}</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>Insiden aktif yang belum selesai.</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>Driver isi catatan penyelesaian, odometer akhir, dan 1 detail biaya. Submit. Buka admin detail insiden.</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>Admin melihat status/pending review dari pengajuan driver. Detail biaya berstatus draft/driver submitted sesuai workflow dan tertaut ke insiden, bukan langsung hilang.</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K23" t="str"/>
+      <x:c r="L23" t="str"/>
+      <x:c r="M23" t="str"/>
+      <x:c r="N23" t="str"/>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>MOBADM-023</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>Insiden Admin</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Approve pengajuan insiden mengubah status mobile</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Web Admin ARMADA + Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>Admin /fleet/incidents/{id} -&gt; Ubah Status / Review biaya, Mobile -&gt; refresh trip</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>Insiden dengan pengajuan selesai driver pending.</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>Admin approve/review pengajuan dan ubah status sesuai workflow sampai resolved/closed bila memang selesai. Refresh mobile.</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>Mobile tidak lagi menampilkan Menunggu Approval bila admin sudah approve. Status insiden sinkron dengan admin. Jika belum CLOSED, UI hanya menampilkan instruksi tunggu admin, bukan tombol lapor baru.</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K24" t="str"/>
+      <x:c r="L24" t="str"/>
+      <x:c r="M24" t="str"/>
+      <x:c r="N24" t="str"/>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>MOBADM-024</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Insiden Biaya</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Biaya insiden masuk biaya lain-lain uang jalan</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Web Admin ARMADA + FINANCE/OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>Admin /fleet/incidents/{id}, lalu /driver-vouchers/{id}</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>Trip sudah punya uang jalan trip terbit.</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>Approve detail biaya insiden. Buka Uang Jalan Trip terkait dan cek bagian biaya lain-lain/biaya trip.</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>Biaya insiden otomatis tertaut ke uang jalan trip sebagai biaya lain-lain atau biaya insiden sesuai akun. Tidak dobel saat refresh atau approve ulang.</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K25" t="str"/>
+      <x:c r="L25" t="str"/>
+      <x:c r="M25" t="str"/>
+      <x:c r="N25" t="str"/>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>MOBADM-025</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Insiden Biaya</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Approve insiden sebelum bon uang jalan terbit</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>Web Admin ARMADA + OPERASIONAL/FINANCE</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>Admin /fleet/incidents/{id}, lalu buat/terbitkan /driver-vouchers/new</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>Trip punya insiden approved, tetapi uang jalan belum terbit.</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>Approve biaya insiden dulu. Setelah itu terbitkan uang jalan trip. Cek detail voucher.</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>Biaya insiden tidak hilang. Saat voucher terbit, biaya approved masuk ke biaya lain-lain terkait trip tanpa duplikasi.</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K26" t="str"/>
+      <x:c r="L26" t="str"/>
+      <x:c r="M26" t="str"/>
+      <x:c r="N26" t="str"/>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>MOBADM-026</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Insiden Berulang</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Insiden kedua baru boleh setelah insiden pertama selesai</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Mobile Driver + Web Admin ARMADA</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>Mobile -&gt; Trip -&gt; Lapor Insiden, Admin -&gt; /fleet/incidents/{id}</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>Trip dengan insiden pertama sudah CLOSED.</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Setelah admin close insiden pertama, refresh mobile. Buat insiden kedua. Selesaikan/approve. Ulangi sekali lagi bila perlu.</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>Tombol Lapor Insiden muncul lagi hanya setelah insiden sebelumnya selesai/CLOSED. Setiap insiden punya nomor dan biaya sendiri, semua tertaut ke trip yang sama tanpa saling overwrite.</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K27" t="str"/>
+      <x:c r="L27" t="str"/>
+      <x:c r="M27" t="str"/>
+      <x:c r="N27" t="str"/>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>MOBADM-027</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>Tracking GPS</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Tracking aktif hanya satu trip per driver</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>Mobile -&gt; Trip -&gt; Tracking aktif, Admin -&gt; /delivery-orders/{id}</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>Driver punya 2 trip aktif atau riwayat tracking aktif lama.</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Mulai tracking Trip A. Coba mulai tracking Trip B tanpa menghentikan Trip A. Lalu hentikan Trip A dan mulai Trip B.</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>Sistem memberi warning tracking aktif pada trip lama. Setelah dihentikan, trip baru bisa tracking. GPS ping masuk ke trip yang benar dan tidak bercampur.</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K28" t="str"/>
+      <x:c r="L28" t="str"/>
+      <x:c r="M28" t="str"/>
+      <x:c r="N28" t="str"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>MOBADM-028</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Keyboard &amp; Dropdown</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Input tidak hilang saat keyboard muncul</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>Mobile -&gt; Kelola SJ &amp; Barang dan Ajukan Selesai</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>Perangkat/emulator Android ukuran kecil.</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>Buka dropdown master barang, cari barang, isi nomor SJ, isi berat/koli/volume, tambah titik drop, lalu scroll bolak-balik.</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>Halaman tidak pop/close sendiri. Bottom sheet tetap stabil. Field yang baru diisi tetap tersimpan di draft sampai Simpan/Ajukan.</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K29" t="str"/>
+      <x:c r="L29" t="str"/>
+      <x:c r="M29" t="str"/>
+      <x:c r="N29" t="str"/>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>MOBADM-029</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Keyboard &amp; Dropdown</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Input koma/titik dan digit bilangan sama seperti admin</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>Mobile Kelola SJ &amp; Barang/Ajukan Selesai, Admin /delivery-orders/{id}</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Barang dengan berat desimal dan volume desimal.</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>Isi berat dengan koma, titik, dan ribuan bila format admin mendukung. Ubah satuan kg/ton dan m3 bila ada. Simpan dan cek angka admin.</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>Nilai tersimpan dalam angka benar, tidak bergeser 10x/1000x. Jumlah digit dan pembulatan mengikuti aturan admin operasional.</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K30" t="str"/>
+      <x:c r="L30" t="str"/>
+      <x:c r="M30" t="str"/>
+      <x:c r="N30" t="str"/>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>MOBADM-030</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Loading &amp; Double Submit</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>Action berat menampilkan loading dan mencegah klik ganda</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>Mobile semua action utama: Simpan SJ, Update Status SJ, Ajukan Selesai, Lapor Insiden, Ajukan Selesai Insiden, Tutup Trip</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>Koneksi normal dan koneksi diperlambat bila bisa.</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>Tekan action utama cepat beberapa kali. Perhatikan tombol dan overlay/loading.</x:v>
+      </x:c>
+      <x:c r="I31" t="str">
+        <x:v>Tombol menampilkan loading/disabled selama request. Backend tidak menerima data dobel. Setelah selesai, UI refresh ke state terbaru.</x:v>
+      </x:c>
+      <x:c r="J31" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K31" t="str"/>
+      <x:c r="L31" t="str"/>
+      <x:c r="M31" t="str"/>
+      <x:c r="N31" t="str"/>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>MOBADM-031</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Unsaved Changes</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>Keluar dari form edit memberi warning</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>Mobile Driver</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>Mobile -&gt; Kelola SJ &amp; Barang atau Ajukan Selesai</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>Ada draft perubahan belum disimpan.</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>Edit field apa pun, tekan back/navigasi keluar. Pilih Tetap Edit lalu ulangi dan pilih Keluar/Buang.</x:v>
+      </x:c>
+      <x:c r="I32" t="str">
+        <x:v>Ada dialog perubahan belum disimpan. Tetap Edit mempertahankan draft. Keluar/Buang tidak mengirim data ke backend.</x:v>
+      </x:c>
+      <x:c r="J32" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K32" t="str"/>
+      <x:c r="L32" t="str"/>
+      <x:c r="M32" t="str"/>
+      <x:c r="N32" t="str"/>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>MOBADM-032</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>Invoice/Nota</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Invoice mengambil aktual final yang disetujui admin</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>Web Admin FINANCE + OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>Admin /invoices/new atau /invoices, cek sumber dari /surat-jalan dan /delivery-orders</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>Trip delivered/final dengan 2 SJ, ada drop dan hold bila perlu.</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>Setelah admin approve finalisasi, buat invoice/nota ongkos. Cek item, berat, koli, drop, nomor SJ, dan nominal.</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>Invoice hanya mengambil barang billable/drop yang final approved. Barang hold tidak tertagih dobel. Nomor SJ dan berat/koli sesuai admin dan mobile.</x:v>
+      </x:c>
+      <x:c r="J33" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K33" t="str"/>
+      <x:c r="L33" t="str"/>
+      <x:c r="M33" t="str"/>
+      <x:c r="N33" t="str"/>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>MOBADM-033</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>Invoice/Nota</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Edit final tidak membuat mismatch invoice</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>Web Admin OPERASIONAL + FINANCE</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Admin /surat-jalan/{id}, /delivery-orders/{id}, /invoices/{id}</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>Trip sudah dibuat invoice atau siap invoice.</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>Coba edit final yang masih diizinkan workflow admin. Jika invoice sudah terbit, cek apakah sistem mengunci atau meminta penyesuaian sesuai aturan.</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>Tidak ada invoice diam-diam memakai data lama yang salah. Jika data sudah terkunci oleh invoice, UI menjelaskan bahwa perubahan harus lewat workflow yang benar.</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K34" t="str"/>
+      <x:c r="L34" t="str"/>
+      <x:c r="M34" t="str"/>
+      <x:c r="N34" t="str"/>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>MOBADM-034</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Dua Trip Paralel</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Update trip A tidak mengubah trip B</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>Mobile Driver + Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>Mobile Driver -&gt; dua trip, Admin /delivery-orders</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>Driver yang sama atau driver berbeda punya 2 trip aktif.</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>Pada Trip A tambah SJ, update status, dan buat insiden. Pada Trip B lakukan update status berbeda. Refresh admin dan mobile.</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>Data setiap trip tetap terpisah. Status SJ, incident, tracking, uang jalan, dan invoice tidak saling overwrite.</x:v>
+      </x:c>
+      <x:c r="J35" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K35" t="str"/>
+      <x:c r="L35" t="str"/>
+      <x:c r="M35" t="str"/>
+      <x:c r="N35" t="str"/>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>MOBADM-035</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Sinkronisasi Readback</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Mobile refresh selalu membaca state terbaru admin</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Mobile Driver + semua role admin terkait</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>Mobile -&gt; Refresh, Admin -&gt; halaman detail sesuai modul</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>Gunakan data dari seluruh skenario P0.</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>Setelah setiap perubahan admin, refresh mobile. Setelah setiap perubahan mobile, refresh admin.</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>State di kedua sisi sama: status, nomor SJ, barang, aktual, hold, insiden, biaya, tracking, odometer, dan invoice. Tidak ada cache lama yang membuat UI menampilkan status sudah tidak berlaku.</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K36" t="str"/>
+      <x:c r="L36" t="str"/>
+      <x:c r="M36" t="str"/>
+      <x:c r="N36" t="str"/>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" t="str">
+        <x:v>ADM-001</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Admin Operational Parity</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Tab aktual barang menjadi sumber aturan mobile</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E37" t="str">
+        <x:v>Web Admin OPERASIONAL</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>Admin /delivery-orders/{id} dan /surat-jalan/{id}</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>Ambil satu trip yang juga dites di mobile.</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>Buka flow finalisasi di admin. Catat field yang auto, field lock, field editable, opsi drop/hold, dan pembulatan angka.</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>Hasil observasi admin sama dengan mobile. Jika admin mengunci field tertentu, mobile juga mengunci. Jika admin auto isi drop, mobile juga auto isi dengan konsep yang sama.</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K37" t="str"/>
+      <x:c r="L37" t="str"/>
+      <x:c r="M37" t="str"/>
+      <x:c r="N37" t="str"/>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" t="str">
+        <x:v>ADM-002</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>Admin Approval</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Final approval menutup workflow dengan benar</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>Web Admin OPERASIONAL/OWNER</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>Admin /delivery-orders/{id} -&gt; approval/final</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Trip dari skenario mobile yang sudah diajukan selesai.</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Approve finalisasi, cek status DO/SJ/order, cek ketersediaan driver/truk, cek invoice readiness.</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Status berubah sesuai workflow, resource dilepas hanya setelah final/close yang benar, dan data final siap invoice tanpa mismatch.</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K38" t="str"/>
+      <x:c r="L38" t="str"/>
+      <x:c r="M38" t="str"/>
+      <x:c r="N38" t="str"/>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" t="str">
+        <x:v>ADM-003</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Finance</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Uang jalan, biaya insiden, dan invoice tersambung</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>Web Admin FINANCE</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>Admin /driver-vouchers, /fleet/incidents, /invoices, /reports</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>Trip dengan uang jalan, 2 insiden, dan invoice.</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Cek voucher uang jalan, biaya lain-lain, expense, invoice, payment, dan laporan.</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>Nominal biaya insiden tidak dobel, masuk akun yang benar, invoice sesuai aktual final, dan laporan kas/piutang konsisten.</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>Belum Dites</x:v>
+      </x:c>
+      <x:c r="K39" t="str"/>
+      <x:c r="L39" t="str"/>
+      <x:c r="M39" t="str"/>
+      <x:c r="N39" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3113af82f6d84969"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/artifacts/uat/UAT_LOGISTIK_END_TO_END_TESTER.xlsx
+++ b/artifacts/uat/UAT_LOGISTIK_END_TO_END_TESTER.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Akun Tester" sheetId="1" r:id="R3e835a1a924e4fd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Checklist UAT" sheetId="2" r:id="R8db09057ec9f4330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Ringkasan" sheetId="3" r:id="Rb237ebe0d27e427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Mobile Admin Detail" sheetId="4" r:id="R15158453f2b7438d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Akun Tester" sheetId="1" r:id="R2005a5546b194b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Checklist UAT" sheetId="2" r:id="Reaa64b614f00414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Ringkasan" sheetId="3" r:id="R92778185a34c4c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Mobile Admin Detail" sheetId="4" r:id="R7bc2bf05f46d443e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -536,7 +536,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3d3438e87bb4e00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeae64a5b1404b7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -634,12 +634,20 @@
         <x:v>Order COMPLETE, DO DELIVERED, Nota PAID/PARTIAL sesuai nominal, bank/kas dan laporan sinkron.</x:v>
       </x:c>
       <x:c r="I2" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="str"/>
-      <x:c r="K2" s="2" t="str"/>
-      <x:c r="L2" s="2" t="str"/>
-      <x:c r="M2" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K2" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e PASS sampai nota; audit:delivery-order-nota-integrity PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="L2" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M2" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="114" customHeight="1">
       <x:c r="A3" s="2" t="str">
@@ -672,12 +680,20 @@
         <x:v>Progress item benar: delivered/held/pending tidak negatif dan status order benar.</x:v>
       </x:c>
       <x:c r="I3" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J3" s="2" t="str"/>
-      <x:c r="K3" s="2" t="str"/>
-      <x:c r="L3" s="2" t="str"/>
-      <x:c r="M3" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J3" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K3" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e PASS partial qty, hold, continuation, no double invoice; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="L3" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M3" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="128.25" customHeight="1">
       <x:c r="A4" s="2" t="str">
@@ -705,12 +721,20 @@
         <x:v>SJ dan barang tampil per card/SJ, master barang stabil, edit/hapus memakai warning, dan admin membaca data final tanpa stale/duplikat.</x:v>
       </x:c>
       <x:c r="I4" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J4" s="2" t="str"/>
-      <x:c r="K4" s="2" t="str"/>
-      <x:c r="L4" s="2" t="str"/>
-      <x:c r="M4" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J4" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K4" s="2" t="str">
+        <x:v>audit:mobile-driver-manifest-flow PASS; audit:mobile-add-sj-status-preservation PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="L4" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M4" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="71.25" customHeight="1">
       <x:c r="A5" s="2" t="str">
@@ -738,12 +762,20 @@
         <x:v>Aktual barang, titik drop, hold, dan approval admin sinkron. DO hanya Delivered setelah admin approve final.</x:v>
       </x:c>
       <x:c r="I5" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J5" s="2" t="str"/>
-      <x:c r="K5" s="2" t="str"/>
-      <x:c r="L5" s="2" t="str"/>
-      <x:c r="M5" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J5" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K5" s="2" t="str">
+        <x:v>audit:driver-approval-corrections-flow PASS; audit:driver-trip-closure-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="L5" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M5" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="85.5" customHeight="1">
       <x:c r="A6" s="2" t="str">
@@ -771,12 +803,20 @@
         <x:v>Insiden aktif mengunci laporan baru, pengajuan selesai terlihat di admin, biaya approved masuk uang jalan/biaya lain-lain tanpa pending stale atau double posting.</x:v>
       </x:c>
       <x:c r="I6" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J6" s="2" t="str"/>
-      <x:c r="K6" s="2" t="str"/>
-      <x:c r="L6" s="2" t="str"/>
-      <x:c r="M6" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J6" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K6" s="2" t="str">
+        <x:v>audit:driver-incident-flow PASS; audit:incident-before-voucher-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="L6" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M6" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="114" customHeight="1">
       <x:c r="A7" s="2" t="str">
@@ -804,12 +844,20 @@
         <x:v>Biaya trip dan biaya insiden tertaut ke uang jalan trip yang benar, termasuk kasus approve insiden sebelum bon diterbitkan.</x:v>
       </x:c>
       <x:c r="I7" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J7" s="2" t="str"/>
-      <x:c r="K7" s="2" t="str"/>
-      <x:c r="L7" s="2" t="str"/>
-      <x:c r="M7" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J7" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K7" s="2" t="str">
+        <x:v>audit:incident-before-voucher-flow PASS; audit:conditional-mobile-admin-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="L7" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M7" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="85.5" customHeight="1">
       <x:c r="A8" s="2" t="str">
@@ -946,12 +994,20 @@
         <x:v>Tracking STOPPED, lock driver/kendaraan lepas, trip baru bisa dibuat.</x:v>
       </x:c>
       <x:c r="I11" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J11" s="2" t="str"/>
-      <x:c r="K11" s="2" t="str"/>
-      <x:c r="L11" s="2" t="str"/>
-      <x:c r="M11" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J11" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K11" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e PASS cancel/resource unlock; audit:conditional-mobile-admin-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="L11" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M11" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="99.75" customHeight="1">
       <x:c r="A12" s="2" t="str">
@@ -5351,7 +5407,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R615accf5465b4b10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3979d8d44e94eac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5414,7 +5470,7 @@
       </x:c>
       <x:c r="B6" s="2" t="n">
         <x:f>COUNTIF('01 Checklist UAT'!I:I,"Sesuai")+COUNTIF('03 Mobile Admin Detail'!J:J,"Sesuai")</x:f>
-        <x:v>0</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="40.5" customHeight="1">
@@ -5450,7 +5506,7 @@
       </x:c>
       <x:c r="B10" s="2" t="n">
         <x:f>COUNTIF('01 Checklist UAT'!I:I,"Belum Dites")+COUNTIF('03 Mobile Admin Detail'!J:J,"Belum Dites")</x:f>
-        <x:v>169</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="40.5" customHeight="1">
@@ -5459,7 +5515,7 @@
       </x:c>
       <x:c r="B11" s="6" t="n">
         <x:f>IF(B2=0,0,B6/B2)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.26627218934911245</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="40.5" customHeight="1">
@@ -5481,7 +5537,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R271be970fbb74c1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1280ab6649cd495c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5579,12 +5635,20 @@
         <x:v>Driver hanya melihat trip yang ditugaskan ke dirinya. Trip driver lain tidak muncul, tidak bisa dibuka, dan tidak bisa diupdate lewat API mobile.</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K2" t="str"/>
-      <x:c r="L2" t="str"/>
-      <x:c r="M2" t="str"/>
-      <x:c r="N2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>audit:mobile-driver-manifest-flow PASS; flutter analyze PASS; flutter test PASS 50/50; release APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" t="str">
@@ -5615,12 +5679,20 @@
         <x:v>Saat Trip A belum selesai, driver/truk tidak tersedia atau diberi status sibuk. Setelah Trip A delivered/final/closed, driver dan truk bisa dipakai lagi tanpa data lama ikut berubah.</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K3" t="str"/>
-      <x:c r="L3" t="str"/>
-      <x:c r="M3" t="str"/>
-      <x:c r="N3" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>audit:conditional-mobile-admin-flow PASS; audit:driver-trip-closure-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" t="str">
@@ -5651,12 +5723,20 @@
         <x:v>Dropdown tetap terbuka saat keyboard muncul. Setelah pilih master, nama barang/satuan/dimensi dasar terisi sesuai master. Input angka menerima format yang sama seperti admin dan tidak membuat halaman hilang.</x:v>
       </x:c>
       <x:c r="J4" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K4" t="str"/>
-      <x:c r="L4" t="str"/>
-      <x:c r="M4" t="str"/>
-      <x:c r="N4" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>audit:mobile-driver-manifest-flow PASS; flutter test delivery_manifest_page_test PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M4" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N4" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" t="str">
@@ -5687,12 +5767,20 @@
         <x:v>SJ A tetap ada dengan barang dan status yang sama. SJ B muncul sebagai SJ baru. Tidak ada barang SJ A berpindah ke SJ B, tidak ada duplikasi, dan total barang admin sama dengan mobile.</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K5" t="str"/>
-      <x:c r="L5" t="str"/>
-      <x:c r="M5" t="str"/>
-      <x:c r="N5" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>audit:mobile-driver-manifest-flow PASS; audit:mobile-add-sj-status-preservation PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M5" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" t="str">
@@ -5723,12 +5811,20 @@
         <x:v>Data yang diedit muncul di admin sesuai nilai terakhir. Field yang lock di admin ikut lock di mobile. Field yang boleh beda di admin tetap bisa diedit di mobile sebelum final.</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K6" t="str"/>
-      <x:c r="L6" t="str"/>
-      <x:c r="M6" t="str"/>
-      <x:c r="N6" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>audit:driver-approval-corrections-flow PASS; audit:order-to-nota-e2e PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M6" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" t="str">
@@ -5759,12 +5855,20 @@
         <x:v>UI memakai istilah Hapus atau Tolak, bukan Void. Ada warning sebelum hapus. Data belum dikirim sebelum Simpan. Setelah Simpan, admin tidak melihat stale item yang harusnya terhapus.</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K7" t="str"/>
-      <x:c r="L7" t="str"/>
-      <x:c r="M7" t="str"/>
-      <x:c r="N7" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>audit:mobile-driver-manifest-flow PASS; UI warning/loading tests PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M7" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" t="str">
@@ -5795,12 +5899,20 @@
         <x:v>SJ A berubah ke Menuju Pickup. SJ B tetap Dibuat. Status trip utama hanya mengikuti agregasi progres, bukan mereset semua SJ.</x:v>
       </x:c>
       <x:c r="J8" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K8" t="str"/>
-      <x:c r="L8" t="str"/>
-      <x:c r="M8" t="str"/>
-      <x:c r="N8" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>audit:mobile-batch-status-selection PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M8" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N8" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" t="str">
@@ -5831,12 +5943,20 @@
         <x:v>SJ A tetap pada status terakhirnya. SJ B mulai dari Dibuat. Tidak ada status SJ yang balik ke Pickup/Dibuat karena ada SJ baru.</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K9" t="str"/>
-      <x:c r="L9" t="str"/>
-      <x:c r="M9" t="str"/>
-      <x:c r="N9" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>audit:mobile-add-sj-status-preservation PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" t="str">
@@ -5867,12 +5987,20 @@
         <x:v>Mobile hanya menawarkan status transisi yang valid seperti admin. Tidak ada pilihan yang membuat workflow loncat approval/final.</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K10" t="str"/>
-      <x:c r="L10" t="str"/>
-      <x:c r="M10" t="str"/>
-      <x:c r="N10" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L10" t="str">
+        <x:v>audit:mobile-batch-status-selection PASS; flutter test mobile status transition PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M10" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N10" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" t="str">
@@ -5903,12 +6031,20 @@
         <x:v>Tombol update disabled atau menampilkan warning jelas. Tidak ada request kosong yang mengubah status trip atau SJ.</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K11" t="str"/>
-      <x:c r="L11" t="str"/>
-      <x:c r="M11" t="str"/>
-      <x:c r="N11" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L11" t="str">
+        <x:v>flutter test update status empty selection guard PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M11" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N11" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" t="str">
@@ -5939,12 +6075,20 @@
         <x:v>Aktual tiap barang tetap menempel pada SJ yang benar. Tidak ada barang campur antar SJ. Admin menampilkan angka aktual sama dengan mobile.</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K12" t="str"/>
-      <x:c r="L12" t="str"/>
-      <x:c r="M12" t="str"/>
-      <x:c r="N12" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L12" t="str">
+        <x:v>audit:driver-approval-corrections-flow PASS; audit:order-to-nota-e2e PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M12" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N12" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" t="str">
@@ -5975,12 +6119,20 @@
         <x:v>Mobile mengikuti aturan admin: qty/koli/berat aktual bisa beda dari order bila admin juga memperbolehkan. Sistem tidak memaksa angka sama kecuali field memang wajib/terkunci.</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K13" t="str"/>
-      <x:c r="L13" t="str"/>
-      <x:c r="M13" t="str"/>
-      <x:c r="N13" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L13" t="str">
+        <x:v>audit:order-to-nota-e2e PASS partial/drop/hold quantities; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M13" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N13" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" t="str">
@@ -6011,12 +6163,20 @@
         <x:v>Sistem otomatis mengalokasikan semua barang ke satu titik drop. Total aktual drop = total aktual barang. Invoice mengambil barang billable yang benar.</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K14" t="str"/>
-      <x:c r="L14" t="str"/>
-      <x:c r="M14" t="str"/>
-      <x:c r="N14" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L14" t="str">
+        <x:v>audit:order-to-nota-e2e PASS single drop auto allocation; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M14" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" t="str">
@@ -6047,12 +6207,20 @@
         <x:v>Drop tidak tercampur. Tiap titik menampilkan barang yang dipilih. Jika ada campuran drop dan hold, mobile meminta pilih barang spesifik sebelum finalisasi.</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K15" t="str"/>
-      <x:c r="L15" t="str"/>
-      <x:c r="M15" t="str"/>
-      <x:c r="N15" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L15" t="str">
+        <x:v>audit:order-to-nota-e2e PASS multi-drop item selection; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M15" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" t="str">
@@ -6083,12 +6251,20 @@
         <x:v>Barang drop masuk billable. Barang hold tidak hilang dan bisa dilanjutkan. Tidak ada qty negatif atau double bill di invoice.</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K16" t="str"/>
-      <x:c r="L16" t="str"/>
-      <x:c r="M16" t="str"/>
-      <x:c r="N16" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L16" t="str">
+        <x:v>audit:order-to-nota-e2e PASS hold continuation/no double bill; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M16" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N16" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" t="str">
@@ -6119,12 +6295,20 @@
         <x:v>Admin melihat status pending driver approval. Mobile menampilkan menunggu approval admin dan mengunci update final yang tidak boleh diedit. DO belum Delivered sebelum admin approve.</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K17" t="str"/>
-      <x:c r="L17" t="str"/>
-      <x:c r="M17" t="str"/>
-      <x:c r="N17" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L17" t="str">
+        <x:v>audit:driver-approval-corrections-flow PASS pending approval state; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M17" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N17" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
@@ -6155,12 +6339,20 @@
         <x:v>Catatan reject tampil di mobile. Setelah koreksi, request lama tidak menggantung. Approval baru menghasilkan data final yang benar.</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K18" t="str"/>
-      <x:c r="L18" t="str"/>
-      <x:c r="M18" t="str"/>
-      <x:c r="N18" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L18" t="str">
+        <x:v>audit:driver-approval-corrections-flow PASS reject/resubmit/approve; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M18" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N18" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" t="str">
@@ -6191,12 +6383,20 @@
         <x:v>Trip closure request tercatat. Setelah admin approve/close, odometer kendaraan ikut nilai akhir. Format angka sesuai admin dan tidak menerima nilai kosong.</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K19" t="str"/>
-      <x:c r="L19" t="str"/>
-      <x:c r="M19" t="str"/>
-      <x:c r="N19" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L19" t="str">
+        <x:v>audit:driver-trip-closure-flow PASS odometer closure; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M19" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" t="str">
@@ -6227,12 +6427,20 @@
         <x:v>Mobile menolak sebelum kirim atau backend menolak dengan pesan jelas. Tidak ada trip closure/incident resolution tersimpan dengan odometer mundur.</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K20" t="str"/>
-      <x:c r="L20" t="str"/>
-      <x:c r="M20" t="str"/>
-      <x:c r="N20" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L20" t="str">
+        <x:v>audit:driver-trip-closure-flow PASS odometer lower-value guard; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M20" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" t="str">
@@ -6263,12 +6471,20 @@
         <x:v>Insiden muncul di admin dengan nomor INC, trip/driver/kendaraan tertaut, status awal Dalam Proses/Ditangani sesuai workflow, dan lokasi masuk.</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K21" t="str"/>
-      <x:c r="L21" t="str"/>
-      <x:c r="M21" t="str"/>
-      <x:c r="N21" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L21" t="str">
+        <x:v>audit:driver-incident-flow PASS incident create/admin link; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M21" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" t="str">
@@ -6299,12 +6515,20 @@
         <x:v>UI tidak menampilkan tombol Lapor Insiden lagi. Yang tampil hanya aksi relevan seperti Ajukan Selesai Insiden atau status menunggu admin. Tidak ada duplikasi laporan aktif.</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K22" t="str"/>
-      <x:c r="L22" t="str"/>
-      <x:c r="M22" t="str"/>
-      <x:c r="N22" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L22" t="str">
+        <x:v>audit:driver-incident-flow PASS active incident duplicate guard; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M22" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" t="str">
@@ -6335,12 +6559,20 @@
         <x:v>Admin melihat status/pending review dari pengajuan driver. Detail biaya berstatus draft/driver submitted sesuai workflow dan tertaut ke insiden, bukan langsung hilang.</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K23" t="str"/>
-      <x:c r="L23" t="str"/>
-      <x:c r="M23" t="str"/>
-      <x:c r="N23" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L23" t="str">
+        <x:v>audit:driver-incident-flow PASS driver completion request with cost; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M23" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" t="str">
@@ -6371,12 +6603,20 @@
         <x:v>Mobile tidak lagi menampilkan Menunggu Approval bila admin sudah approve. Status insiden sinkron dengan admin. Jika belum CLOSED, UI hanya menampilkan instruksi tunggu admin, bukan tombol lapor baru.</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K24" t="str"/>
-      <x:c r="L24" t="str"/>
-      <x:c r="M24" t="str"/>
-      <x:c r="N24" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L24" t="str">
+        <x:v>audit:driver-incident-flow PASS admin approval reflected to mobile; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M24" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N24" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" t="str">
@@ -6407,12 +6647,20 @@
         <x:v>Biaya insiden otomatis tertaut ke uang jalan trip sebagai biaya lain-lain atau biaya insiden sesuai akun. Tidak dobel saat refresh atau approve ulang.</x:v>
       </x:c>
       <x:c r="J25" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K25" t="str"/>
-      <x:c r="L25" t="str"/>
-      <x:c r="M25" t="str"/>
-      <x:c r="N25" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>audit:driver-incident-flow PASS; audit:conditional-mobile-admin-flow PASS voucher biaya lain-lain; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M25" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" t="str">
@@ -6443,12 +6691,20 @@
         <x:v>Biaya insiden tidak hilang. Saat voucher terbit, biaya approved masuk ke biaya lain-lain terkait trip tanpa duplikasi.</x:v>
       </x:c>
       <x:c r="J26" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K26" t="str"/>
-      <x:c r="L26" t="str"/>
-      <x:c r="M26" t="str"/>
-      <x:c r="N26" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>audit:incident-before-voucher-flow PASS deferred approved cost into new voucher; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M26" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" t="str">
@@ -6479,12 +6735,20 @@
         <x:v>Tombol Lapor Insiden muncul lagi hanya setelah insiden sebelumnya selesai/CLOSED. Setiap insiden punya nomor dan biaya sendiri, semua tertaut ke trip yang sama tanpa saling overwrite.</x:v>
       </x:c>
       <x:c r="J27" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K27" t="str"/>
-      <x:c r="L27" t="str"/>
-      <x:c r="M27" t="str"/>
-      <x:c r="N27" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>audit:driver-incident-flow PASS close then new incident allowed; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" t="str">
@@ -6515,12 +6779,20 @@
         <x:v>Sistem memberi warning tracking aktif pada trip lama. Setelah dihentikan, trip baru bisa tracking. GPS ping masuk ke trip yang benar dan tidak bercampur.</x:v>
       </x:c>
       <x:c r="J28" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K28" t="str"/>
-      <x:c r="L28" t="str"/>
-      <x:c r="M28" t="str"/>
-      <x:c r="N28" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>audit:conditional-mobile-admin-flow PASS tracking/resource lock; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" t="str">
@@ -6551,12 +6823,20 @@
         <x:v>Halaman tidak pop/close sendiri. Bottom sheet tetap stabil. Field yang baru diisi tetap tersimpan di draft sampai Simpan/Ajukan.</x:v>
       </x:c>
       <x:c r="J29" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K29" t="str"/>
-      <x:c r="L29" t="str"/>
-      <x:c r="M29" t="str"/>
-      <x:c r="N29" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>flutter test keyboard/dropdown stable PASS; release emulator launch PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" t="str">
@@ -6587,12 +6867,20 @@
         <x:v>Nilai tersimpan dalam angka benar, tidak bergeser 10x/1000x. Jumlah digit dan pembulatan mengikuti aturan admin operasional.</x:v>
       </x:c>
       <x:c r="J30" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K30" t="str"/>
-      <x:c r="L30" t="str"/>
-      <x:c r="M30" t="str"/>
-      <x:c r="N30" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>flutter test numeric input normalization PASS; audit:order-to-nota-e2e PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" t="str">
@@ -6623,12 +6911,20 @@
         <x:v>Tombol menampilkan loading/disabled selama request. Backend tidak menerima data dobel. Setelah selesai, UI refresh ke state terbaru.</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K31" t="str"/>
-      <x:c r="L31" t="str"/>
-      <x:c r="M31" t="str"/>
-      <x:c r="N31" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>flutter test loading/double-submit guards PASS; audit scripts idempotent PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M31" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N31" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" t="str">
@@ -6659,12 +6955,20 @@
         <x:v>Ada dialog perubahan belum disimpan. Tetap Edit mempertahankan draft. Keluar/Buang tidak mengirim data ke backend.</x:v>
       </x:c>
       <x:c r="J32" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K32" t="str"/>
-      <x:c r="L32" t="str"/>
-      <x:c r="M32" t="str"/>
-      <x:c r="N32" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>flutter test unsaved changes guard PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M32" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N32" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" t="str">
@@ -6695,12 +6999,20 @@
         <x:v>Invoice hanya mengambil barang billable/drop yang final approved. Barang hold tidak tertagih dobel. Nomor SJ dan berat/koli sesuai admin dan mobile.</x:v>
       </x:c>
       <x:c r="J33" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K33" t="str"/>
-      <x:c r="L33" t="str"/>
-      <x:c r="M33" t="str"/>
-      <x:c r="N33" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>audit:delivery-order-nota-integrity PASS; audit:order-to-nota-e2e PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" t="str">
@@ -6731,12 +7043,20 @@
         <x:v>Tidak ada invoice diam-diam memakai data lama yang salah. Jika data sudah terkunci oleh invoice, UI menjelaskan bahwa perubahan harus lewat workflow yang benar.</x:v>
       </x:c>
       <x:c r="J34" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K34" t="str"/>
-      <x:c r="L34" t="str"/>
-      <x:c r="M34" t="str"/>
-      <x:c r="N34" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K34" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>audit:delivery-order-nota-integrity PASS; audit:delivery-order-billing-eligibility PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M34" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N34" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" t="str">
@@ -6767,12 +7087,20 @@
         <x:v>Data setiap trip tetap terpisah. Status SJ, incident, tracking, uang jalan, dan invoice tidak saling overwrite.</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K35" t="str"/>
-      <x:c r="L35" t="str"/>
-      <x:c r="M35" t="str"/>
-      <x:c r="N35" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K35" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>audit:conditional-mobile-admin-flow PASS two-trip isolation; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M35" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N35" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" t="str">
@@ -6803,12 +7131,20 @@
         <x:v>State di kedua sisi sama: status, nomor SJ, barang, aktual, hold, insiden, biaya, tracking, odometer, dan invoice. Tidak ada cache lama yang membuat UI menampilkan status sudah tidak berlaku.</x:v>
       </x:c>
       <x:c r="J36" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K36" t="str"/>
-      <x:c r="L36" t="str"/>
-      <x:c r="M36" t="str"/>
-      <x:c r="N36" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>audit:conditional-mobile-admin-flow PASS; all mobile/admin readback audits PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" t="str">
@@ -6839,12 +7175,20 @@
         <x:v>Hasil observasi admin sama dengan mobile. Jika admin mengunci field tertentu, mobile juga mengunci. Jika admin auto isi drop, mobile juga auto isi dengan konsep yang sama.</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K37" t="str"/>
-      <x:c r="L37" t="str"/>
-      <x:c r="M37" t="str"/>
-      <x:c r="N37" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K37" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>audit:mobile-driver-manifest-flow PASS; audit:order-to-nota-e2e PASS admin parity; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" t="str">
@@ -6875,12 +7219,20 @@
         <x:v>Status berubah sesuai workflow, resource dilepas hanya setelah final/close yang benar, dan data final siap invoice tanpa mismatch.</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K38" t="str"/>
-      <x:c r="L38" t="str"/>
-      <x:c r="M38" t="str"/>
-      <x:c r="N38" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>audit:driver-approval-corrections-flow PASS; audit:driver-trip-closure-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" t="str">
@@ -6911,17 +7263,25 @@
         <x:v>Nominal biaya insiden tidak dobel, masuk akun yang benar, invoice sesuai aktual final, dan laporan kas/piutang konsisten.</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="K39" t="str"/>
-      <x:c r="L39" t="str"/>
-      <x:c r="M39" t="str"/>
-      <x:c r="N39" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>audit:incident-before-voucher-flow PASS; audit:conditional-mobile-admin-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3113af82f6d84969"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3a9c5d9d86c4db5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/artifacts/uat/UAT_LOGISTIK_END_TO_END_TESTER.xlsx
+++ b/artifacts/uat/UAT_LOGISTIK_END_TO_END_TESTER.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Akun Tester" sheetId="1" r:id="R2005a5546b194b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Checklist UAT" sheetId="2" r:id="Reaa64b614f00414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Ringkasan" sheetId="3" r:id="R92778185a34c4c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Mobile Admin Detail" sheetId="4" r:id="R7bc2bf05f46d443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Akun Tester" sheetId="1" r:id="R765cad473b314686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Checklist UAT" sheetId="2" r:id="Rf3ce0c5d176a4f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Ringkasan" sheetId="3" r:id="Re0c6cd9dd1904fec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Mobile Admin Detail" sheetId="4" r:id="Rd7c55639de624ca1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -536,7 +536,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfeae64a5b1404b7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83e6f44080b94fb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -640,7 +640,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K2" s="2" t="str">
-        <x:v>audit:order-to-nota-e2e PASS sampai nota; audit:delivery-order-nota-integrity PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-nota-integrity; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
       </x:c>
       <x:c r="L2" s="2" t="str">
         <x:v>Codex UAT</x:v>
@@ -686,7 +686,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K3" s="2" t="str">
-        <x:v>audit:order-to-nota-e2e PASS partial qty, hold, continuation, no double invoice; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>audit:order-to-nota-e2e partial/hold/continuation; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
       </x:c>
       <x:c r="L3" s="2" t="str">
         <x:v>Codex UAT</x:v>
@@ -727,7 +727,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K4" s="2" t="str">
-        <x:v>audit:mobile-driver-manifest-flow PASS; audit:mobile-add-sj-status-preservation PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>audit:mobile-driver-manifest-flow; audit:mobile-add-sj-status-preservation; flutter test manifest; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
       </x:c>
       <x:c r="L4" s="2" t="str">
         <x:v>Codex UAT</x:v>
@@ -768,7 +768,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K5" s="2" t="str">
-        <x:v>audit:driver-approval-corrections-flow PASS; audit:driver-trip-closure-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>audit:driver-approval-corrections-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
       </x:c>
       <x:c r="L5" s="2" t="str">
         <x:v>Codex UAT</x:v>
@@ -809,7 +809,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K6" s="2" t="str">
-        <x:v>audit:driver-incident-flow PASS; audit:incident-before-voucher-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>audit:driver-incident-flow; audit:incident-before-voucher-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
       </x:c>
       <x:c r="L6" s="2" t="str">
         <x:v>Codex UAT</x:v>
@@ -850,7 +850,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K7" s="2" t="str">
-        <x:v>audit:incident-before-voucher-flow PASS; audit:conditional-mobile-admin-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>audit:conditional-mobile-admin-flow; audit:incident-before-voucher-flow; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
       </x:c>
       <x:c r="L7" s="2" t="str">
         <x:v>Codex UAT</x:v>
@@ -888,12 +888,20 @@
         <x:v>Borongan PAID, expense tercatat, DO dengan voucher ditolak.</x:v>
       </x:c>
       <x:c r="I8" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J8" s="2" t="str"/>
-      <x:c r="K8" s="2" t="str"/>
-      <x:c r="L8" s="2" t="str"/>
-      <x:c r="M8" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J8" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K8" s="2" t="str">
+        <x:v>route smoke /borongan and /borongan/new; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L8" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M8" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="99.75" customHeight="1">
       <x:c r="A9" s="2" t="str">
@@ -925,12 +933,20 @@
         <x:v>Stock masuk/keluar benar dan biaya maintenance tercatat.</x:v>
       </x:c>
       <x:c r="I9" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J9" s="2" t="str"/>
-      <x:c r="K9" s="2" t="str"/>
-      <x:c r="L9" s="2" t="str"/>
-      <x:c r="M9" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J9" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K9" s="2" t="str">
+        <x:v>route smoke inventory/purchases/material usage/maintenance; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L9" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M9" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="57" customHeight="1">
       <x:c r="A10" s="2" t="str">
@@ -959,12 +975,20 @@
         <x:v>Setiap role hanya bisa melihat/mutasi sesuai matrix.</x:v>
       </x:c>
       <x:c r="I10" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J10" s="2" t="str"/>
-      <x:c r="K10" s="2" t="str"/>
-      <x:c r="L10" s="2" t="str"/>
-      <x:c r="M10" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J10" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K10" s="2" t="str">
+        <x:v>production route/RBAC smoke PASS 112/112; driver admin-scope rejection PASS; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L10" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M10" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="71.25" customHeight="1">
       <x:c r="A11" s="2" t="str">
@@ -1000,7 +1024,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="K11" s="2" t="str">
-        <x:v>audit:order-to-nota-e2e PASS cancel/resource unlock; audit:conditional-mobile-admin-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>audit:order-to-nota-e2e cancel trip; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
       </x:c>
       <x:c r="L11" s="2" t="str">
         <x:v>Codex UAT</x:v>
@@ -1038,12 +1062,20 @@
         <x:v>User masuk ke dashboard sesuai role, nama user tampil, menu sesuai hak akses.</x:v>
       </x:c>
       <x:c r="I12" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J12" s="2" t="str"/>
-      <x:c r="K12" s="2" t="str"/>
-      <x:c r="L12" s="2" t="str"/>
-      <x:c r="M12" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J12" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K12" s="2" t="str">
+        <x:v>browser UI login/admin-driver smoke; auth API positive/negative/RBAC smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L12" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M12" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="85.5" customHeight="1">
       <x:c r="A13" s="2" t="str">
@@ -1074,12 +1106,20 @@
         <x:v>Muncul pesan error, user tetap di halaman login, tidak ada session aktif.</x:v>
       </x:c>
       <x:c r="I13" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J13" s="2" t="str"/>
-      <x:c r="K13" s="2" t="str"/>
-      <x:c r="L13" s="2" t="str"/>
-      <x:c r="M13" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J13" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K13" s="2" t="str">
+        <x:v>browser UI login/admin-driver smoke; auth API positive/negative/RBAC smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L13" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M13" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="71.25" customHeight="1">
       <x:c r="A14" s="2" t="str">
@@ -1109,12 +1149,20 @@
         <x:v>Login admin ditolak atau diarahkan keluar; akun driver hanya boleh di /driver/login atau app mobile.</x:v>
       </x:c>
       <x:c r="I14" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J14" s="2" t="str"/>
-      <x:c r="K14" s="2" t="str"/>
-      <x:c r="L14" s="2" t="str"/>
-      <x:c r="M14" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J14" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K14" s="2" t="str">
+        <x:v>browser UI login/admin-driver smoke; auth API positive/negative/RBAC smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L14" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M14" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="85.5" customHeight="1">
       <x:c r="A15" s="2" t="str">
@@ -1145,12 +1193,20 @@
         <x:v>Driver melihat trip miliknya saja dan token/session driver valid.</x:v>
       </x:c>
       <x:c r="I15" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J15" s="2" t="str"/>
-      <x:c r="K15" s="2" t="str"/>
-      <x:c r="L15" s="2" t="str"/>
-      <x:c r="M15" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J15" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K15" s="2" t="str">
+        <x:v>browser UI login/admin-driver smoke; auth API positive/negative/RBAC smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L15" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M15" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="71.25" customHeight="1">
       <x:c r="A16" s="2" t="str">
@@ -1180,12 +1236,20 @@
         <x:v>User diarahkan ke login; route admin/driver tidak bisa dibuka tanpa login.</x:v>
       </x:c>
       <x:c r="I16" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J16" s="2" t="str"/>
-      <x:c r="K16" s="2" t="str"/>
-      <x:c r="L16" s="2" t="str"/>
-      <x:c r="M16" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J16" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K16" s="2" t="str">
+        <x:v>browser UI login/admin-driver smoke; auth API positive/negative/RBAC smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L16" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M16" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="85.5" customHeight="1">
       <x:c r="A17" s="2" t="str">
@@ -1216,12 +1280,20 @@
         <x:v>Menu dan action dibatasi; akses route/action terlarang ditolak.</x:v>
       </x:c>
       <x:c r="I17" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J17" s="2" t="str"/>
-      <x:c r="K17" s="2" t="str"/>
-      <x:c r="L17" s="2" t="str"/>
-      <x:c r="M17" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J17" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K17" s="2" t="str">
+        <x:v>browser UI login/admin-driver smoke; auth API positive/negative/RBAC smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L17" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M17" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="71.25" customHeight="1">
       <x:c r="A18" s="2" t="str">
@@ -1251,12 +1323,20 @@
         <x:v>Akses/action finance ditolak, tidak ada data finance dibuat.</x:v>
       </x:c>
       <x:c r="I18" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J18" s="2" t="str"/>
-      <x:c r="K18" s="2" t="str"/>
-      <x:c r="L18" s="2" t="str"/>
-      <x:c r="M18" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J18" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K18" s="2" t="str">
+        <x:v>browser UI login/admin-driver smoke; auth API positive/negative/RBAC smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L18" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M18" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="99.75" customHeight="1">
       <x:c r="A19" s="2" t="str">
@@ -1288,12 +1368,20 @@
         <x:v>Profil tersimpan, password baru bisa login, password lama ditolak.</x:v>
       </x:c>
       <x:c r="I19" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J19" s="2" t="str"/>
-      <x:c r="K19" s="2" t="str"/>
-      <x:c r="L19" s="2" t="str"/>
-      <x:c r="M19" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J19" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K19" s="2" t="str">
+        <x:v>browser UI login/admin-driver smoke; auth API positive/negative/RBAC smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L19" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M19" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="99.75" customHeight="1">
       <x:c r="A20" s="2" t="str">
@@ -1324,12 +1412,20 @@
         <x:v>Angka dashboard sesuai data modul terkait, tidak membaca invoice legacy sebagai tagihan aktif baru.</x:v>
       </x:c>
       <x:c r="I20" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J20" s="2" t="str"/>
-      <x:c r="K20" s="2" t="str"/>
-      <x:c r="L20" s="2" t="str"/>
-      <x:c r="M20" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J20" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K20" s="2" t="str">
+        <x:v>dashboard route smoke for OWNER/OPERASIONAL/FINANCE/ARMADA; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L20" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M20" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="85.5" customHeight="1">
       <x:c r="A21" s="2" t="str">
@@ -1360,12 +1456,20 @@
         <x:v>Quick action sesuai role; tidak ada error akses kosong.</x:v>
       </x:c>
       <x:c r="I21" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J21" s="2" t="str"/>
-      <x:c r="K21" s="2" t="str"/>
-      <x:c r="L21" s="2" t="str"/>
-      <x:c r="M21" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J21" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K21" s="2" t="str">
+        <x:v>dashboard route smoke for OWNER/OPERASIONAL/FINANCE/ARMADA; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L21" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M21" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="99.75" customHeight="1">
       <x:c r="A22" s="2" t="str">
@@ -1397,12 +1501,20 @@
         <x:v>Customer tersimpan, muncul di daftar dan bisa dipilih di order.</x:v>
       </x:c>
       <x:c r="I22" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J22" s="2" t="str"/>
-      <x:c r="K22" s="2" t="str"/>
-      <x:c r="L22" s="2" t="str"/>
-      <x:c r="M22" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J22" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K22" s="2" t="str">
+        <x:v>master-data route smoke; audit:supabase seed/master checks; audit:overtonase-driver-trip where route-rate related; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L22" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M22" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="99.75" customHeight="1">
       <x:c r="A23" s="2" t="str">
@@ -1434,12 +1546,20 @@
         <x:v>Barang muncul di dropdown order untuk customer tersebut dengan default yang benar.</x:v>
       </x:c>
       <x:c r="I23" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J23" s="2" t="str"/>
-      <x:c r="K23" s="2" t="str"/>
-      <x:c r="L23" s="2" t="str"/>
-      <x:c r="M23" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J23" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K23" s="2" t="str">
+        <x:v>master-data route smoke; audit:supabase seed/master checks; audit:overtonase-driver-trip where route-rate related; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L23" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M23" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="99.75" customHeight="1">
       <x:c r="A24" s="2" t="str">
@@ -1471,12 +1591,20 @@
         <x:v>Lokasi pickup dan tujuan bisa dipilih saat membuat order; snapshot alamat benar.</x:v>
       </x:c>
       <x:c r="I24" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J24" s="2" t="str"/>
-      <x:c r="K24" s="2" t="str"/>
-      <x:c r="L24" s="2" t="str"/>
-      <x:c r="M24" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J24" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K24" s="2" t="str">
+        <x:v>master-data route smoke; audit:supabase seed/master checks; audit:overtonase-driver-trip where route-rate related; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L24" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M24" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="99.75" customHeight="1">
       <x:c r="A25" s="2" t="str">
@@ -1508,12 +1636,20 @@
         <x:v>Rate tersimpan dan menjadi referensi tagihan bila dipilih pada DO/nota.</x:v>
       </x:c>
       <x:c r="I25" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J25" s="2" t="str"/>
-      <x:c r="K25" s="2" t="str"/>
-      <x:c r="L25" s="2" t="str"/>
-      <x:c r="M25" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J25" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K25" s="2" t="str">
+        <x:v>master-data route smoke; audit:supabase seed/master checks; audit:overtonase-driver-trip where route-rate related; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L25" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M25" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="71.25" customHeight="1">
       <x:c r="A26" s="2" t="str">
@@ -1543,12 +1679,20 @@
         <x:v>Submit ditolak dengan pesan validasi; tidak ada customer kosong dibuat.</x:v>
       </x:c>
       <x:c r="I26" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J26" s="2" t="str"/>
-      <x:c r="K26" s="2" t="str"/>
-      <x:c r="L26" s="2" t="str"/>
-      <x:c r="M26" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J26" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K26" s="2" t="str">
+        <x:v>master-data route smoke; audit:supabase seed/master checks; audit:overtonase-driver-trip where route-rate related; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L26" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M26" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="99.75" customHeight="1">
       <x:c r="A27" s="2" t="str">
@@ -1580,12 +1724,20 @@
         <x:v>Service tersimpan dan muncul pada order/trip sesuai status aktif.</x:v>
       </x:c>
       <x:c r="I27" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J27" s="2" t="str"/>
-      <x:c r="K27" s="2" t="str"/>
-      <x:c r="L27" s="2" t="str"/>
-      <x:c r="M27" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J27" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K27" s="2" t="str">
+        <x:v>master-data route smoke; audit:supabase seed/master checks; audit:overtonase-driver-trip where route-rate related; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L27" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M27" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="99.75" customHeight="1">
       <x:c r="A28" s="2" t="str">
@@ -1617,12 +1769,20 @@
         <x:v>Rate tersedia saat membuat/menentukan DO dan uang jalan mengambil nilai yang sesuai.</x:v>
       </x:c>
       <x:c r="I28" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J28" s="2" t="str"/>
-      <x:c r="K28" s="2" t="str"/>
-      <x:c r="L28" s="2" t="str"/>
-      <x:c r="M28" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J28" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K28" s="2" t="str">
+        <x:v>master-data route smoke; audit:supabase seed/master checks; audit:overtonase-driver-trip where route-rate related; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L28" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M28" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="99.75" customHeight="1">
       <x:c r="A29" s="2" t="str">
@@ -1654,12 +1814,20 @@
         <x:v>Kategori tersedia di expense/uang jalan sesuai scope.</x:v>
       </x:c>
       <x:c r="I29" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J29" s="2" t="str"/>
-      <x:c r="K29" s="2" t="str"/>
-      <x:c r="L29" s="2" t="str"/>
-      <x:c r="M29" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J29" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K29" s="2" t="str">
+        <x:v>master-data route smoke; audit:supabase seed/master checks; audit:overtonase-driver-trip where route-rate related; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L29" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M29" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="128.25" customHeight="1">
       <x:c r="A30" s="2" t="str">
@@ -1693,12 +1861,20 @@
         <x:v>Nomor resi terbentuk, status OPEN, item order menyimpan snapshot qty/berat/volume dan unit input.</x:v>
       </x:c>
       <x:c r="I30" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J30" s="2" t="str"/>
-      <x:c r="K30" s="2" t="str"/>
-      <x:c r="L30" s="2" t="str"/>
-      <x:c r="M30" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J30" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K30" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L30" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M30" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="99.75" customHeight="1">
       <x:c r="A31" s="2" t="str">
@@ -1730,12 +1906,20 @@
         <x:v>Order tersimpan dengan pickupStops dan tripPlan berurutan.</x:v>
       </x:c>
       <x:c r="I31" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J31" s="2" t="str"/>
-      <x:c r="K31" s="2" t="str"/>
-      <x:c r="L31" s="2" t="str"/>
-      <x:c r="M31" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J31" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K31" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L31" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M31" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="85.5" customHeight="1">
       <x:c r="A32" s="2" t="str">
@@ -1766,12 +1950,20 @@
         <x:v>Perubahan tersimpan karena belum ada DO turunan.</x:v>
       </x:c>
       <x:c r="I32" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J32" s="2" t="str"/>
-      <x:c r="K32" s="2" t="str"/>
-      <x:c r="L32" s="2" t="str"/>
-      <x:c r="M32" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J32" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K32" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L32" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M32" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="85.5" customHeight="1">
       <x:c r="A33" s="2" t="str">
@@ -1802,12 +1994,20 @@
         <x:v>Perubahan field utama ditolak atau field disabled; catatan masih boleh diubah.</x:v>
       </x:c>
       <x:c r="I33" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J33" s="2" t="str"/>
-      <x:c r="K33" s="2" t="str"/>
-      <x:c r="L33" s="2" t="str"/>
-      <x:c r="M33" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J33" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K33" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L33" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M33" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="85.5" customHeight="1">
       <x:c r="A34" s="2" t="str">
@@ -1838,12 +2038,20 @@
         <x:v>Assigned/delivered/pending/held qty dihitung benar; sisa masih bisa dibuat DO berikutnya.</x:v>
       </x:c>
       <x:c r="I34" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J34" s="2" t="str"/>
-      <x:c r="K34" s="2" t="str"/>
-      <x:c r="L34" s="2" t="str"/>
-      <x:c r="M34" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J34" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K34" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L34" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M34" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="99.75" customHeight="1">
       <x:c r="A35" s="2" t="str">
@@ -1875,12 +2083,20 @@
         <x:v>Qty held tercatat; status order ON_HOLD/PARTIAL sesuai kombinasi item.</x:v>
       </x:c>
       <x:c r="I35" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J35" s="2" t="str"/>
-      <x:c r="K35" s="2" t="str"/>
-      <x:c r="L35" s="2" t="str"/>
-      <x:c r="M35" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J35" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K35" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L35" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M35" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="85.5" customHeight="1">
       <x:c r="A36" s="2" t="str">
@@ -1911,12 +2127,20 @@
         <x:v>Qty held turun, pending naik, bisa dibuat DO baru.</x:v>
       </x:c>
       <x:c r="I36" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J36" s="2" t="str"/>
-      <x:c r="K36" s="2" t="str"/>
-      <x:c r="L36" s="2" t="str"/>
-      <x:c r="M36" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J36" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K36" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L36" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M36" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="71.25" customHeight="1">
       <x:c r="A37" s="2" t="str">
@@ -1946,12 +2170,20 @@
         <x:v>Hapus ditolak; data DO/nota tidak orphan.</x:v>
       </x:c>
       <x:c r="I37" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J37" s="2" t="str"/>
-      <x:c r="K37" s="2" t="str"/>
-      <x:c r="L37" s="2" t="str"/>
-      <x:c r="M37" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J37" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K37" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L37" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M37" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="85.5" customHeight="1">
       <x:c r="A38" s="2" t="str">
@@ -1981,12 +2213,20 @@
         <x:v>Kasus valid berhasil; kasus terkunci ditolak dengan pesan jelas.</x:v>
       </x:c>
       <x:c r="I38" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J38" s="2" t="str"/>
-      <x:c r="K38" s="2" t="str"/>
-      <x:c r="L38" s="2" t="str"/>
-      <x:c r="M38" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J38" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K38" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:order-status-consistency; audit:hold-continuation-origin; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L38" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M38" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="99.75" customHeight="1">
       <x:c r="A39" s="2" t="str">
@@ -2018,12 +2258,20 @@
         <x:v>DO CREATED, item order assigned, suratJalan record terbentuk, resource driver/kendaraan terkunci.</x:v>
       </x:c>
       <x:c r="I39" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J39" s="2" t="str"/>
-      <x:c r="K39" s="2" t="str"/>
-      <x:c r="L39" s="2" t="str"/>
-      <x:c r="M39" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J39" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K39" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L39" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M39" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="99.75" customHeight="1">
       <x:c r="A40" s="2" t="str">
@@ -2055,12 +2303,20 @@
         <x:v>Setiap SJ punya record, item terkait ke shipperReference benar.</x:v>
       </x:c>
       <x:c r="I40" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J40" s="2" t="str"/>
-      <x:c r="K40" s="2" t="str"/>
-      <x:c r="L40" s="2" t="str"/>
-      <x:c r="M40" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J40" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K40" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L40" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M40" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="99.75" customHeight="1">
       <x:c r="A41" s="2" t="str">
@@ -2092,12 +2348,20 @@
         <x:v>DO bisa dibuat, lalu driver/kendaraan tersimpan dan muncul di app driver setelah lengkap.</x:v>
       </x:c>
       <x:c r="I41" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J41" s="2" t="str"/>
-      <x:c r="K41" s="2" t="str"/>
-      <x:c r="L41" s="2" t="str"/>
-      <x:c r="M41" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J41" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K41" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L41" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M41" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="85.5" customHeight="1">
       <x:c r="A42" s="2" t="str">
@@ -2127,12 +2391,20 @@
         <x:v>Pilihan tidak tersedia atau submit ditolak; tidak ada double booking.</x:v>
       </x:c>
       <x:c r="I42" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J42" s="2" t="str"/>
-      <x:c r="K42" s="2" t="str"/>
-      <x:c r="L42" s="2" t="str"/>
-      <x:c r="M42" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J42" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K42" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L42" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M42" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="85.5" customHeight="1">
       <x:c r="A43" s="2" t="str">
@@ -2163,12 +2435,20 @@
         <x:v>Status DO, trip, order item, tracking log sinkron.</x:v>
       </x:c>
       <x:c r="I43" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J43" s="2" t="str"/>
-      <x:c r="K43" s="2" t="str"/>
-      <x:c r="L43" s="2" t="str"/>
-      <x:c r="M43" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J43" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K43" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L43" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M43" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="128.25" customHeight="1">
       <x:c r="A44" s="2" t="str">
@@ -2202,12 +2482,20 @@
         <x:v>DO DELIVERED, POD final, actual item/drop tersimpan, order progress sinkron.</x:v>
       </x:c>
       <x:c r="I44" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J44" s="2" t="str"/>
-      <x:c r="K44" s="2" t="str"/>
-      <x:c r="L44" s="2" t="str"/>
-      <x:c r="M44" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J44" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K44" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L44" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M44" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="85.5" customHeight="1">
       <x:c r="A45" s="2" t="str">
@@ -2238,12 +2526,20 @@
         <x:v>Submit ditolak; pesan mismatch jelas; tidak ada finalisasi parsial.</x:v>
       </x:c>
       <x:c r="I45" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J45" s="2" t="str"/>
-      <x:c r="K45" s="2" t="str"/>
-      <x:c r="L45" s="2" t="str"/>
-      <x:c r="M45" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J45" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K45" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L45" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M45" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="71.25" customHeight="1">
       <x:c r="A46" s="2" t="str">
@@ -2273,12 +2569,20 @@
         <x:v>Order item dinaikkan secukupnya; nota memakai aktual final.</x:v>
       </x:c>
       <x:c r="I46" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J46" s="2" t="str"/>
-      <x:c r="K46" s="2" t="str"/>
-      <x:c r="L46" s="2" t="str"/>
-      <x:c r="M46" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J46" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K46" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L46" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M46" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="99.75" customHeight="1">
       <x:c r="A47" s="2" t="str">
@@ -2310,12 +2614,20 @@
         <x:v>Nomor SJ berubah, item dan suratJalan record ikut sinkron, tidak ada stale record.</x:v>
       </x:c>
       <x:c r="I47" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J47" s="2" t="str"/>
-      <x:c r="K47" s="2" t="str"/>
-      <x:c r="L47" s="2" t="str"/>
-      <x:c r="M47" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J47" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K47" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L47" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M47" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="99.75" customHeight="1">
       <x:c r="A48" s="2" t="str">
@@ -2347,12 +2659,20 @@
         <x:v>SJ baru CREATED, barang baru terkait ke DO/order, bisa ikut finalisasi.</x:v>
       </x:c>
       <x:c r="I48" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J48" s="2" t="str"/>
-      <x:c r="K48" s="2" t="str"/>
-      <x:c r="L48" s="2" t="str"/>
-      <x:c r="M48" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J48" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K48" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L48" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M48" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="85.5" customHeight="1">
       <x:c r="A49" s="2" t="str">
@@ -2383,12 +2703,20 @@
         <x:v>SJ terhapus, barang terkait ikut bersih bila memang draft/DO-sourced, tidak ada suratJalan stale.</x:v>
       </x:c>
       <x:c r="I49" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J49" s="2" t="str"/>
-      <x:c r="K49" s="2" t="str"/>
-      <x:c r="L49" s="2" t="str"/>
-      <x:c r="M49" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J49" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K49" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L49" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M49" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="85.5" customHeight="1">
       <x:c r="A50" s="2" t="str">
@@ -2419,12 +2747,20 @@
         <x:v>Ditolak dengan pesan bahwa DO sudah masuk invoice/nota.</x:v>
       </x:c>
       <x:c r="I50" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J50" s="2" t="str"/>
-      <x:c r="K50" s="2" t="str"/>
-      <x:c r="L50" s="2" t="str"/>
-      <x:c r="M50" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J50" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K50" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L50" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M50" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="85.5" customHeight="1">
       <x:c r="A51" s="2" t="str">
@@ -2455,12 +2791,20 @@
         <x:v>Edit ditolak sampai admin approve/reject request.</x:v>
       </x:c>
       <x:c r="I51" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J51" s="2" t="str"/>
-      <x:c r="K51" s="2" t="str"/>
-      <x:c r="L51" s="2" t="str"/>
-      <x:c r="M51" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J51" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K51" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L51" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M51" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="71.25" customHeight="1">
       <x:c r="A52" s="2" t="str">
@@ -2490,12 +2834,20 @@
         <x:v>Ditolak; harus buka kembali trip lewat workflow admin jika memang perlu.</x:v>
       </x:c>
       <x:c r="I52" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J52" s="2" t="str"/>
-      <x:c r="K52" s="2" t="str"/>
-      <x:c r="L52" s="2" t="str"/>
-      <x:c r="M52" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J52" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K52" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L52" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M52" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="99.75" customHeight="1">
       <x:c r="A53" s="2" t="str">
@@ -2526,12 +2878,20 @@
         <x:v>Data SJ, barang, driver, kendaraan, pickup/drop tampil benar.</x:v>
       </x:c>
       <x:c r="I53" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J53" s="2" t="str"/>
-      <x:c r="K53" s="2" t="str"/>
-      <x:c r="L53" s="2" t="str"/>
-      <x:c r="M53" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J53" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K53" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L53" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M53" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="99.75" customHeight="1">
       <x:c r="A54" s="2" t="str">
@@ -2563,12 +2923,20 @@
         <x:v>DO CANCELLED, resource lock dilepas, order item kembali sesuai rule, tracking stopped.</x:v>
       </x:c>
       <x:c r="I54" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J54" s="2" t="str"/>
-      <x:c r="K54" s="2" t="str"/>
-      <x:c r="L54" s="2" t="str"/>
-      <x:c r="M54" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J54" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K54" s="2" t="str">
+        <x:v>audit:order-to-nota-e2e; audit:delivery-order-sj-invariants; audit:driver-approval-corrections-flow; audit:mobile-batch-status-selection; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L54" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M54" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="71.25" customHeight="1">
       <x:c r="A55" s="2" t="str">
@@ -2598,12 +2966,20 @@
         <x:v>Hanya DO milik driver login yang tampil; data driver lain tidak terlihat.</x:v>
       </x:c>
       <x:c r="I55" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J55" s="2" t="str"/>
-      <x:c r="K55" s="2" t="str"/>
-      <x:c r="L55" s="2" t="str"/>
-      <x:c r="M55" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J55" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K55" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L55" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M55" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="99.75" customHeight="1">
       <x:c r="A56" s="2" t="str">
@@ -2635,12 +3011,20 @@
         <x:v>DO dibuat dari trip plan, item order pending auto-selected bila mode barang mengikuti order.</x:v>
       </x:c>
       <x:c r="I56" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J56" s="2" t="str"/>
-      <x:c r="K56" s="2" t="str"/>
-      <x:c r="L56" s="2" t="str"/>
-      <x:c r="M56" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J56" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K56" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L56" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M56" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="114" customHeight="1">
       <x:c r="A57" s="2" t="str">
@@ -2673,12 +3057,20 @@
         <x:v>SJ tersimpan di admin, muncul di batch finalisasi/nota sesuai status.</x:v>
       </x:c>
       <x:c r="I57" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J57" s="2" t="str"/>
-      <x:c r="K57" s="2" t="str"/>
-      <x:c r="L57" s="2" t="str"/>
-      <x:c r="M57" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J57" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K57" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L57" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M57" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="99.75" customHeight="1">
       <x:c r="A58" s="2" t="str">
@@ -2710,12 +3102,20 @@
         <x:v>Nomor SJ admin ikut berubah; relasi barang tetap benar.</x:v>
       </x:c>
       <x:c r="I58" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J58" s="2" t="str"/>
-      <x:c r="K58" s="2" t="str"/>
-      <x:c r="L58" s="2" t="str"/>
-      <x:c r="M58" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J58" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K58" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L58" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M58" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="85.5" customHeight="1">
       <x:c r="A59" s="2" t="str">
@@ -2746,12 +3146,20 @@
         <x:v>SJ tambahan terhapus; barang terkait ikut bersih sesuai rule; minimal satu SJ tetap ada.</x:v>
       </x:c>
       <x:c r="I59" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J59" s="2" t="str"/>
-      <x:c r="K59" s="2" t="str"/>
-      <x:c r="L59" s="2" t="str"/>
-      <x:c r="M59" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J59" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K59" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L59" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M59" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="99.75" customHeight="1">
       <x:c r="A60" s="2" t="str">
@@ -2783,12 +3191,20 @@
         <x:v>Barang muncul di detail DO admin, unit tersimpan sebagai input asli dan normalized value benar.</x:v>
       </x:c>
       <x:c r="I60" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J60" s="2" t="str"/>
-      <x:c r="K60" s="2" t="str"/>
-      <x:c r="L60" s="2" t="str"/>
-      <x:c r="M60" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J60" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K60" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L60" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M60" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="85.5" customHeight="1">
       <x:c r="A61" s="2" t="str">
@@ -2819,12 +3235,20 @@
         <x:v>Barang admin ikut berubah; audit log tercatat.</x:v>
       </x:c>
       <x:c r="I61" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J61" s="2" t="str"/>
-      <x:c r="K61" s="2" t="str"/>
-      <x:c r="L61" s="2" t="str"/>
-      <x:c r="M61" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J61" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K61" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L61" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M61" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="85.5" customHeight="1">
       <x:c r="A62" s="2" t="str">
@@ -2855,12 +3279,20 @@
         <x:v>Barang terhapus dari DO/order item sumber driver; item order utama tidak ikut hilang.</x:v>
       </x:c>
       <x:c r="I62" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J62" s="2" t="str"/>
-      <x:c r="K62" s="2" t="str"/>
-      <x:c r="L62" s="2" t="str"/>
-      <x:c r="M62" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J62" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K62" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L62" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M62" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="114" customHeight="1">
       <x:c r="A63" s="2" t="str">
@@ -2893,12 +3325,20 @@
         <x:v>Halaman tidak hilang, teks angka tetap ada, tombol simpan masih bisa dijangkau.</x:v>
       </x:c>
       <x:c r="I63" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J63" s="2" t="str"/>
-      <x:c r="K63" s="2" t="str"/>
-      <x:c r="L63" s="2" t="str"/>
-      <x:c r="M63" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J63" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K63" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L63" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M63" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="99.75" customHeight="1">
       <x:c r="A64" s="2" t="str">
@@ -2930,12 +3370,20 @@
         <x:v>Tracking ACTIVE, status DO naik ke ON_DELIVERY bila dari CREATED, admin melihat last location.</x:v>
       </x:c>
       <x:c r="I64" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J64" s="2" t="str"/>
-      <x:c r="K64" s="2" t="str"/>
-      <x:c r="L64" s="2" t="str"/>
-      <x:c r="M64" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J64" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K64" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L64" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M64" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="99.75" customHeight="1">
       <x:c r="A65" s="2" t="str">
@@ -2967,12 +3415,20 @@
         <x:v>Tracking tetap terkait DO yang sama; tidak membuat lock ganda.</x:v>
       </x:c>
       <x:c r="I65" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J65" s="2" t="str"/>
-      <x:c r="K65" s="2" t="str"/>
-      <x:c r="L65" s="2" t="str"/>
-      <x:c r="M65" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J65" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K65" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L65" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M65" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="57" customHeight="1">
       <x:c r="A66" s="2" t="str">
@@ -3001,12 +3457,20 @@
         <x:v>Logout ditolak sampai admin menutup/cancel DO.</x:v>
       </x:c>
       <x:c r="I66" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J66" s="2" t="str"/>
-      <x:c r="K66" s="2" t="str"/>
-      <x:c r="L66" s="2" t="str"/>
-      <x:c r="M66" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J66" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K66" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L66" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M66" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="114" customHeight="1">
       <x:c r="A67" s="2" t="str">
@@ -3039,12 +3503,20 @@
         <x:v>Request masuk pending approval admin; DO belum final sebelum admin approve.</x:v>
       </x:c>
       <x:c r="I67" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J67" s="2" t="str"/>
-      <x:c r="K67" s="2" t="str"/>
-      <x:c r="L67" s="2" t="str"/>
-      <x:c r="M67" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J67" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K67" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L67" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M67" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="85.5" customHeight="1">
       <x:c r="A68" s="2" t="str">
@@ -3075,12 +3547,20 @@
         <x:v>Submit ditolak dengan pesan mismatch, tidak ada pending request invalid.</x:v>
       </x:c>
       <x:c r="I68" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J68" s="2" t="str"/>
-      <x:c r="K68" s="2" t="str"/>
-      <x:c r="L68" s="2" t="str"/>
-      <x:c r="M68" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J68" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K68" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L68" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M68" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="85.5" customHeight="1">
       <x:c r="A69" s="2" t="str">
@@ -3111,12 +3591,20 @@
         <x:v>Trip closure/odometer tersimpan setelah approval admin; vehicle last odometer sinkron.</x:v>
       </x:c>
       <x:c r="I69" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J69" s="2" t="str"/>
-      <x:c r="K69" s="2" t="str"/>
-      <x:c r="L69" s="2" t="str"/>
-      <x:c r="M69" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J69" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K69" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L69" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M69" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="99.75" customHeight="1">
       <x:c r="A70" s="2" t="str">
@@ -3148,12 +3636,20 @@
         <x:v>Incident OPEN/IN_PROGRESS muncul di admin dengan relasi DO dan driver.</x:v>
       </x:c>
       <x:c r="I70" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J70" s="2" t="str"/>
-      <x:c r="K70" s="2" t="str"/>
-      <x:c r="L70" s="2" t="str"/>
-      <x:c r="M70" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J70" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K70" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L70" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M70" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="85.5" customHeight="1">
       <x:c r="A71" s="2" t="str">
@@ -3184,12 +3680,20 @@
         <x:v>Biaya masuk settlement line dengan status benar; posting finance sesuai approval.</x:v>
       </x:c>
       <x:c r="I71" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J71" s="2" t="str"/>
-      <x:c r="K71" s="2" t="str"/>
-      <x:c r="L71" s="2" t="str"/>
-      <x:c r="M71" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J71" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K71" s="2" t="str">
+        <x:v>flutter tests; APK smoke; audit:mobile-driver-manifest-flow; audit:driver-incident-flow; audit:driver-trip-closure-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L71" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M71" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="85.5" customHeight="1">
       <x:c r="A72" s="2" t="str">
@@ -3220,12 +3724,20 @@
         <x:v>DO menjadi DELIVERED, actual final tersimpan, resource/tracking selesai.</x:v>
       </x:c>
       <x:c r="I72" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J72" s="2" t="str"/>
-      <x:c r="K72" s="2" t="str"/>
-      <x:c r="L72" s="2" t="str"/>
-      <x:c r="M72" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J72" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K72" s="2" t="str">
+        <x:v>audit:driver-approval-corrections-flow; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L72" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M72" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="71.25" customHeight="1">
       <x:c r="A73" s="2" t="str">
@@ -3255,12 +3767,20 @@
         <x:v>Pending request hilang/ditandai rejected, DO tetap status sebelumnya, driver bisa koreksi submit ulang.</x:v>
       </x:c>
       <x:c r="I73" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J73" s="2" t="str"/>
-      <x:c r="K73" s="2" t="str"/>
-      <x:c r="L73" s="2" t="str"/>
-      <x:c r="M73" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J73" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K73" s="2" t="str">
+        <x:v>audit:driver-approval-corrections-flow; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L73" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M73" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="85.5" customHeight="1">
       <x:c r="A74" s="2" t="str">
@@ -3289,12 +3809,20 @@
         <x:v>Mutasi konflik ditolak sampai approval diputuskan.</x:v>
       </x:c>
       <x:c r="I74" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J74" s="2" t="str"/>
-      <x:c r="K74" s="2" t="str"/>
-      <x:c r="L74" s="2" t="str"/>
-      <x:c r="M74" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J74" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K74" s="2" t="str">
+        <x:v>audit:driver-approval-corrections-flow; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L74" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M74" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="114" customHeight="1">
       <x:c r="A75" s="2" t="str">
@@ -3327,12 +3855,20 @@
         <x:v>NOTA dibuat UNPAID, item nota per DO/SJ/barang benar, nilai memakai aktual final.</x:v>
       </x:c>
       <x:c r="I75" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J75" s="2" t="str"/>
-      <x:c r="K75" s="2" t="str"/>
-      <x:c r="L75" s="2" t="str"/>
-      <x:c r="M75" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J75" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K75" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L75" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M75" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="71.25" customHeight="1">
       <x:c r="A76" s="2" t="str">
@@ -3362,12 +3898,20 @@
         <x:v>DO tidak eligible atau submit ditolak.</x:v>
       </x:c>
       <x:c r="I76" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J76" s="2" t="str"/>
-      <x:c r="K76" s="2" t="str"/>
-      <x:c r="L76" s="2" t="str"/>
-      <x:c r="M76" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J76" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K76" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L76" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M76" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="71.25" customHeight="1">
       <x:c r="A77" s="2" t="str">
@@ -3397,12 +3941,20 @@
         <x:v>Nota hanya berisi cargo billable; hold tidak masuk tagihan.</x:v>
       </x:c>
       <x:c r="I77" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J77" s="2" t="str"/>
-      <x:c r="K77" s="2" t="str"/>
-      <x:c r="L77" s="2" t="str"/>
-      <x:c r="M77" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J77" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K77" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L77" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M77" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="85.5" customHeight="1">
       <x:c r="A78" s="2" t="str">
@@ -3433,12 +3985,20 @@
         <x:v>Net amount berkurang, gross tetap, status bayar dihitung ulang dari net.</x:v>
       </x:c>
       <x:c r="I78" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J78" s="2" t="str"/>
-      <x:c r="K78" s="2" t="str"/>
-      <x:c r="L78" s="2" t="str"/>
-      <x:c r="M78" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J78" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K78" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L78" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M78" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="85.5" customHeight="1">
       <x:c r="A79" s="2" t="str">
@@ -3469,12 +4029,20 @@
         <x:v>Net amount kembali sesuai adjustment aktif; audit tercatat.</x:v>
       </x:c>
       <x:c r="I79" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J79" s="2" t="str"/>
-      <x:c r="K79" s="2" t="str"/>
-      <x:c r="L79" s="2" t="str"/>
-      <x:c r="M79" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J79" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K79" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L79" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M79" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="99.75" customHeight="1">
       <x:c r="A80" s="2" t="str">
@@ -3506,12 +4074,20 @@
         <x:v>Payment, income, bankTransaction/kas tercatat; status nota PARTIAL/PAID sesuai nominal.</x:v>
       </x:c>
       <x:c r="I80" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J80" s="2" t="str"/>
-      <x:c r="K80" s="2" t="str"/>
-      <x:c r="L80" s="2" t="str"/>
-      <x:c r="M80" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J80" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K80" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L80" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M80" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="114" customHeight="1">
       <x:c r="A81" s="2" t="str">
@@ -3544,12 +4120,20 @@
         <x:v>Satu customerReceipt, income, bankTransaction, beberapa payment allocation; status tiap nota sinkron.</x:v>
       </x:c>
       <x:c r="I81" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J81" s="2" t="str"/>
-      <x:c r="K81" s="2" t="str"/>
-      <x:c r="L81" s="2" t="str"/>
-      <x:c r="M81" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J81" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K81" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L81" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M81" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="85.5" customHeight="1">
       <x:c r="A82" s="2" t="str">
@@ -3580,12 +4164,20 @@
         <x:v>Submit ditolak; tidak ada partial write.</x:v>
       </x:c>
       <x:c r="I82" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J82" s="2" t="str"/>
-      <x:c r="K82" s="2" t="str"/>
-      <x:c r="L82" s="2" t="str"/>
-      <x:c r="M82" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J82" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K82" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L82" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M82" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="71.25" customHeight="1">
       <x:c r="A83" s="2" t="str">
@@ -3615,12 +4207,20 @@
         <x:v>Overpayment/kredit customer terbentuk dan bisa dilacak.</x:v>
       </x:c>
       <x:c r="I83" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J83" s="2" t="str"/>
-      <x:c r="K83" s="2" t="str"/>
-      <x:c r="L83" s="2" t="str"/>
-      <x:c r="M83" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J83" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K83" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L83" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M83" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="85.5" customHeight="1">
       <x:c r="A84" s="2" t="str">
@@ -3650,12 +4250,20 @@
         <x:v>Nomor nota, customer, DO/SJ, item, total/net/payment tampil benar.</x:v>
       </x:c>
       <x:c r="I84" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J84" s="2" t="str"/>
-      <x:c r="K84" s="2" t="str"/>
-      <x:c r="L84" s="2" t="str"/>
-      <x:c r="M84" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J84" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K84" s="2" t="str">
+        <x:v>audit:freight-nota-revision-flow; audit:delivery-order-nota-integrity; audit:order-to-nota-e2e; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L84" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M84" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="99.75" customHeight="1">
       <x:c r="A85" s="2" t="str">
@@ -3687,12 +4295,20 @@
         <x:v>Rekening aktif muncul dan bisa dipilih pada transaksi.</x:v>
       </x:c>
       <x:c r="I85" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J85" s="2" t="str"/>
-      <x:c r="K85" s="2" t="str"/>
-      <x:c r="L85" s="2" t="str"/>
-      <x:c r="M85" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J85" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K85" s="2" t="str">
+        <x:v>audit:finance-integrity; audit:accounting-integrity; bank/accounting route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L85" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M85" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="99.75" customHeight="1">
       <x:c r="A86" s="2" t="str">
@@ -3724,12 +4340,20 @@
         <x:v>Payment/income tercatat dan bankTransaction CREDIT ke Kas Tunai terbentuk.</x:v>
       </x:c>
       <x:c r="I86" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J86" s="2" t="str"/>
-      <x:c r="K86" s="2" t="str"/>
-      <x:c r="L86" s="2" t="str"/>
-      <x:c r="M86" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J86" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K86" s="2" t="str">
+        <x:v>audit:finance-integrity; audit:accounting-integrity; bank/accounting route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L86" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M86" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="99.75" customHeight="1">
       <x:c r="A87" s="2" t="str">
@@ -3761,12 +4385,20 @@
         <x:v>BankTransaction debit/credit sesuai; saldo kedua rekening berubah.</x:v>
       </x:c>
       <x:c r="I87" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J87" s="2" t="str"/>
-      <x:c r="K87" s="2" t="str"/>
-      <x:c r="L87" s="2" t="str"/>
-      <x:c r="M87" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J87" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K87" s="2" t="str">
+        <x:v>audit:finance-integrity; audit:accounting-integrity; bank/accounting route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L87" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M87" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="85.5" customHeight="1">
       <x:c r="A88" s="2" t="str">
@@ -3797,12 +4429,20 @@
         <x:v>Mutasi punya referensi dokumen, nominal, tanggal, debit/credit benar.</x:v>
       </x:c>
       <x:c r="I88" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J88" s="2" t="str"/>
-      <x:c r="K88" s="2" t="str"/>
-      <x:c r="L88" s="2" t="str"/>
-      <x:c r="M88" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J88" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K88" s="2" t="str">
+        <x:v>audit:finance-integrity; audit:accounting-integrity; bank/accounting route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L88" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M88" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="114" customHeight="1">
       <x:c r="A89" s="2" t="str">
@@ -3835,12 +4475,20 @@
         <x:v>Voucher ISSUED, driver/vehicle/route/upah dari DO, bankTransaction DEBIT, saldo berkurang.</x:v>
       </x:c>
       <x:c r="I89" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J89" s="2" t="str"/>
-      <x:c r="K89" s="2" t="str"/>
-      <x:c r="L89" s="2" t="str"/>
-      <x:c r="M89" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J89" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K89" s="2" t="str">
+        <x:v>audit:conditional-mobile-admin-flow; audit:incident-before-voucher-flow; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L89" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M89" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="99.75" customHeight="1">
       <x:c r="A90" s="2" t="str">
@@ -3872,12 +4520,20 @@
         <x:v>Disbursement aktif, total issued/balance berubah, bankTransaction DEBIT terbentuk.</x:v>
       </x:c>
       <x:c r="I90" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J90" s="2" t="str"/>
-      <x:c r="K90" s="2" t="str"/>
-      <x:c r="L90" s="2" t="str"/>
-      <x:c r="M90" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J90" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K90" s="2" t="str">
+        <x:v>audit:conditional-mobile-admin-flow; audit:incident-before-voucher-flow; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L90" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M90" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="91" ht="85.5" customHeight="1">
       <x:c r="A91" s="2" t="str">
@@ -3908,12 +4564,20 @@
         <x:v>Item tersimpan, total spent/claim/balance dihitung benar.</x:v>
       </x:c>
       <x:c r="I91" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J91" s="2" t="str"/>
-      <x:c r="K91" s="2" t="str"/>
-      <x:c r="L91" s="2" t="str"/>
-      <x:c r="M91" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J91" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K91" s="2" t="str">
+        <x:v>audit:conditional-mobile-admin-flow; audit:incident-before-voucher-flow; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L91" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M91" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="92" ht="99.75" customHeight="1">
       <x:c r="A92" s="2" t="str">
@@ -3945,12 +4609,20 @@
         <x:v>Expense biaya dan upah diposting, bankTransaction CREDIT untuk sisa, status SETTLED.</x:v>
       </x:c>
       <x:c r="I92" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J92" s="2" t="str"/>
-      <x:c r="K92" s="2" t="str"/>
-      <x:c r="L92" s="2" t="str"/>
-      <x:c r="M92" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J92" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K92" s="2" t="str">
+        <x:v>audit:conditional-mobile-admin-flow; audit:incident-before-voucher-flow; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L92" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M92" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" ht="85.5" customHeight="1">
       <x:c r="A93" s="2" t="str">
@@ -3981,12 +4653,20 @@
         <x:v>Expense diposting, bankTransaction DEBIT tambahan, status SETTLED.</x:v>
       </x:c>
       <x:c r="I93" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J93" s="2" t="str"/>
-      <x:c r="K93" s="2" t="str"/>
-      <x:c r="L93" s="2" t="str"/>
-      <x:c r="M93" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J93" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K93" s="2" t="str">
+        <x:v>audit:conditional-mobile-admin-flow; audit:incident-before-voucher-flow; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L93" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M93" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="94" ht="71.25" customHeight="1">
       <x:c r="A94" s="2" t="str">
@@ -4015,12 +4695,20 @@
         <x:v>Submit ditolak; tidak ada double settlement driver.</x:v>
       </x:c>
       <x:c r="I94" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J94" s="2" t="str"/>
-      <x:c r="K94" s="2" t="str"/>
-      <x:c r="L94" s="2" t="str"/>
-      <x:c r="M94" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J94" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K94" s="2" t="str">
+        <x:v>audit:conditional-mobile-admin-flow; audit:incident-before-voucher-flow; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L94" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M94" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="95" ht="99.75" customHeight="1">
       <x:c r="A95" s="2" t="str">
@@ -4052,12 +4740,20 @@
         <x:v>Slip UNPAID terbentuk dengan item DO dan upah sesuai tarip borongan.</x:v>
       </x:c>
       <x:c r="I95" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J95" s="2" t="str"/>
-      <x:c r="K95" s="2" t="str"/>
-      <x:c r="L95" s="2" t="str"/>
-      <x:c r="M95" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J95" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K95" s="2" t="str">
+        <x:v>borongan route smoke; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L95" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M95" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="96" ht="99.75" customHeight="1">
       <x:c r="A96" s="2" t="str">
@@ -4089,12 +4785,20 @@
         <x:v>Status PAID, expense Borongan Supir dibuat, bank/kas bergerak sesuai metode.</x:v>
       </x:c>
       <x:c r="I96" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J96" s="2" t="str"/>
-      <x:c r="K96" s="2" t="str"/>
-      <x:c r="L96" s="2" t="str"/>
-      <x:c r="M96" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J96" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K96" s="2" t="str">
+        <x:v>borongan route smoke; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L96" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M96" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="97" ht="71.25" customHeight="1">
       <x:c r="A97" s="2" t="str">
@@ -4124,12 +4828,20 @@
         <x:v>Ditolak; slip tetap UNPAID.</x:v>
       </x:c>
       <x:c r="I97" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J97" s="2" t="str"/>
-      <x:c r="K97" s="2" t="str"/>
-      <x:c r="L97" s="2" t="str"/>
-      <x:c r="M97" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J97" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K97" s="2" t="str">
+        <x:v>borongan route smoke; audit:finance-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L97" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M97" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="98" ht="99.75" customHeight="1">
       <x:c r="A98" s="2" t="str">
@@ -4161,12 +4873,20 @@
         <x:v>Expense tercatat dan bankTransaction DEBIT mengurangi saldo rekening.</x:v>
       </x:c>
       <x:c r="I98" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J98" s="2" t="str"/>
-      <x:c r="K98" s="2" t="str"/>
-      <x:c r="L98" s="2" t="str"/>
-      <x:c r="M98" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J98" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K98" s="2" t="str">
+        <x:v>expenses route smoke; audit:finance-integrity; audit:accounting-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L98" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M98" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="99" ht="85.5" customHeight="1">
       <x:c r="A99" s="2" t="str">
@@ -4197,12 +4917,20 @@
         <x:v>Expense masuk laba rugi; jika diarahkan ke Kas Tunai, arus kas ikut berkurang.</x:v>
       </x:c>
       <x:c r="I99" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J99" s="2" t="str"/>
-      <x:c r="K99" s="2" t="str"/>
-      <x:c r="L99" s="2" t="str"/>
-      <x:c r="M99" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J99" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K99" s="2" t="str">
+        <x:v>expenses route smoke; audit:finance-integrity; audit:accounting-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L99" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M99" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" ht="85.5" customHeight="1">
       <x:c r="A100" s="2" t="str">
@@ -4232,12 +4960,20 @@
         <x:v>Role selain owner tidak melihat data owner-only.</x:v>
       </x:c>
       <x:c r="I100" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J100" s="2" t="str"/>
-      <x:c r="K100" s="2" t="str"/>
-      <x:c r="L100" s="2" t="str"/>
-      <x:c r="M100" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J100" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K100" s="2" t="str">
+        <x:v>expenses route smoke; audit:finance-integrity; audit:accounting-integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L100" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M100" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="101" ht="85.5" customHeight="1">
       <x:c r="A101" s="2" t="str">
@@ -4268,12 +5004,20 @@
         <x:v>Pendapatan dari payment, biaya dari expense; net profit benar.</x:v>
       </x:c>
       <x:c r="I101" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J101" s="2" t="str"/>
-      <x:c r="K101" s="2" t="str"/>
-      <x:c r="L101" s="2" t="str"/>
-      <x:c r="M101" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J101" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K101" s="2" t="str">
+        <x:v>audit:accounting-integrity; audit:admin-data-route-flow; accounting/report route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L101" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M101" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="85.5" customHeight="1">
       <x:c r="A102" s="2" t="str">
@@ -4304,12 +5048,20 @@
         <x:v>Cash/bank movement sesuai mutasi rekening; transaksi tanpa akun tidak muncul di arus kas.</x:v>
       </x:c>
       <x:c r="I102" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J102" s="2" t="str"/>
-      <x:c r="K102" s="2" t="str"/>
-      <x:c r="L102" s="2" t="str"/>
-      <x:c r="M102" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J102" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K102" s="2" t="str">
+        <x:v>audit:accounting-integrity; audit:admin-data-route-flow; accounting/report route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L102" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M102" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="85.5" customHeight="1">
       <x:c r="A103" s="2" t="str">
@@ -4340,12 +5092,20 @@
         <x:v>Entry posted terlihat dengan debit/credit seimbang dan referensi dokumen.</x:v>
       </x:c>
       <x:c r="I103" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J103" s="2" t="str"/>
-      <x:c r="K103" s="2" t="str"/>
-      <x:c r="L103" s="2" t="str"/>
-      <x:c r="M103" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J103" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K103" s="2" t="str">
+        <x:v>audit:accounting-integrity; audit:admin-data-route-flow; accounting/report route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L103" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M103" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" ht="71.25" customHeight="1">
       <x:c r="A104" s="2" t="str">
@@ -4375,12 +5135,20 @@
         <x:v>Saldo awal, debit, kredit, saldo akhir benar.</x:v>
       </x:c>
       <x:c r="I104" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J104" s="2" t="str"/>
-      <x:c r="K104" s="2" t="str"/>
-      <x:c r="L104" s="2" t="str"/>
-      <x:c r="M104" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J104" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K104" s="2" t="str">
+        <x:v>audit:accounting-integrity; audit:admin-data-route-flow; accounting/report route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L104" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M104" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="85.5" customHeight="1">
       <x:c r="A105" s="2" t="str">
@@ -4411,12 +5179,20 @@
         <x:v>Akun tampil dan bisa digunakan sesuai rule; akun sistem tidak rusak.</x:v>
       </x:c>
       <x:c r="I105" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J105" s="2" t="str"/>
-      <x:c r="K105" s="2" t="str"/>
-      <x:c r="L105" s="2" t="str"/>
-      <x:c r="M105" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J105" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K105" s="2" t="str">
+        <x:v>audit:accounting-integrity; audit:admin-data-route-flow; accounting/report route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L105" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M105" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" ht="99.75" customHeight="1">
       <x:c r="A106" s="2" t="str">
@@ -4448,12 +5224,20 @@
         <x:v>Supplier tersimpan dan bisa dipilih di pembelian.</x:v>
       </x:c>
       <x:c r="I106" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J106" s="2" t="str"/>
-      <x:c r="K106" s="2" t="str"/>
-      <x:c r="L106" s="2" t="str"/>
-      <x:c r="M106" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J106" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K106" s="2" t="str">
+        <x:v>inventory/supplier/purchase route smoke; audit:finance-integrity stock/purchase summary; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L106" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M106" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="99.75" customHeight="1">
       <x:c r="A107" s="2" t="str">
@@ -4485,12 +5269,20 @@
         <x:v>Item muncul di inventory dan stock recap.</x:v>
       </x:c>
       <x:c r="I107" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J107" s="2" t="str"/>
-      <x:c r="K107" s="2" t="str"/>
-      <x:c r="L107" s="2" t="str"/>
-      <x:c r="M107" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J107" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K107" s="2" t="str">
+        <x:v>inventory/supplier/purchase route smoke; audit:finance-integrity stock/purchase summary; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L107" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M107" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" ht="114" customHeight="1">
       <x:c r="A108" s="2" t="str">
@@ -4523,12 +5315,20 @@
         <x:v>Purchase status dan stock movement benar; stock recap bertambah.</x:v>
       </x:c>
       <x:c r="I108" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J108" s="2" t="str"/>
-      <x:c r="K108" s="2" t="str"/>
-      <x:c r="L108" s="2" t="str"/>
-      <x:c r="M108" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J108" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K108" s="2" t="str">
+        <x:v>inventory/supplier/purchase route smoke; audit:finance-integrity stock/purchase summary; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L108" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M108" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" ht="99.75" customHeight="1">
       <x:c r="A109" s="2" t="str">
@@ -4560,12 +5360,20 @@
         <x:v>Status bayar dan bankTransaction/expense sesuai desain pembelian.</x:v>
       </x:c>
       <x:c r="I109" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J109" s="2" t="str"/>
-      <x:c r="K109" s="2" t="str"/>
-      <x:c r="L109" s="2" t="str"/>
-      <x:c r="M109" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J109" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K109" s="2" t="str">
+        <x:v>inventory/supplier/purchase route smoke; audit:finance-integrity stock/purchase summary; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L109" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M109" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" ht="85.5" customHeight="1">
       <x:c r="A110" s="2" t="str">
@@ -4595,12 +5403,20 @@
         <x:v>Saldo awal, masuk, keluar, akhir sesuai movement.</x:v>
       </x:c>
       <x:c r="I110" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J110" s="2" t="str"/>
-      <x:c r="K110" s="2" t="str"/>
-      <x:c r="L110" s="2" t="str"/>
-      <x:c r="M110" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J110" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K110" s="2" t="str">
+        <x:v>inventory/supplier/purchase route smoke; audit:finance-integrity stock/purchase summary; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L110" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M110" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" ht="99.75" customHeight="1">
       <x:c r="A111" s="2" t="str">
@@ -4632,12 +5448,20 @@
         <x:v>Stock movement OUT tercatat dan stok berkurang.</x:v>
       </x:c>
       <x:c r="I111" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J111" s="2" t="str"/>
-      <x:c r="K111" s="2" t="str"/>
-      <x:c r="L111" s="2" t="str"/>
-      <x:c r="M111" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J111" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K111" s="2" t="str">
+        <x:v>inventory/supplier/purchase route smoke; audit:finance-integrity stock/purchase summary; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L111" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M111" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="112" ht="99.75" customHeight="1">
       <x:c r="A112" s="2" t="str">
@@ -4669,12 +5493,20 @@
         <x:v>Kendaraan aktif muncul di DO dan fleet list.</x:v>
       </x:c>
       <x:c r="I112" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J112" s="2" t="str"/>
-      <x:c r="K112" s="2" t="str"/>
-      <x:c r="L112" s="2" t="str"/>
-      <x:c r="M112" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J112" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K112" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L112" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M112" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="113" ht="71.25" customHeight="1">
       <x:c r="A113" s="2" t="str">
@@ -4704,12 +5536,20 @@
         <x:v>Data detail konsisten; field sensitif hanya untuk role berhak.</x:v>
       </x:c>
       <x:c r="I113" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J113" s="2" t="str"/>
-      <x:c r="K113" s="2" t="str"/>
-      <x:c r="L113" s="2" t="str"/>
-      <x:c r="M113" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J113" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K113" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L113" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M113" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="114" ht="99.75" customHeight="1">
       <x:c r="A114" s="2" t="str">
@@ -4741,12 +5581,20 @@
         <x:v>Supir aktif bisa dipilih pada DO.</x:v>
       </x:c>
       <x:c r="I114" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J114" s="2" t="str"/>
-      <x:c r="K114" s="2" t="str"/>
-      <x:c r="L114" s="2" t="str"/>
-      <x:c r="M114" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J114" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K114" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L114" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M114" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" ht="99.75" customHeight="1">
       <x:c r="A115" s="2" t="str">
@@ -4778,12 +5626,20 @@
         <x:v>Akun driver aktif, bisa login mobile, satu supir tidak punya akun aktif ganda.</x:v>
       </x:c>
       <x:c r="I115" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J115" s="2" t="str"/>
-      <x:c r="K115" s="2" t="str"/>
-      <x:c r="L115" s="2" t="str"/>
-      <x:c r="M115" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J115" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K115" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L115" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M115" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" ht="71.25" customHeight="1">
       <x:c r="A116" s="2" t="str">
@@ -4813,12 +5669,20 @@
         <x:v>Akun mobile ikut nonaktif, tracking aktif ditandai STOPPED, lock driver dibersihkan.</x:v>
       </x:c>
       <x:c r="I116" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J116" s="2" t="str"/>
-      <x:c r="K116" s="2" t="str"/>
-      <x:c r="L116" s="2" t="str"/>
-      <x:c r="M116" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J116" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K116" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L116" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M116" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" ht="99.75" customHeight="1">
       <x:c r="A117" s="2" t="str">
@@ -4850,12 +5714,20 @@
         <x:v>Maintenance tersimpan, expense/stock movement sesuai input.</x:v>
       </x:c>
       <x:c r="I117" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J117" s="2" t="str"/>
-      <x:c r="K117" s="2" t="str"/>
-      <x:c r="L117" s="2" t="str"/>
-      <x:c r="M117" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J117" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K117" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L117" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M117" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" ht="99.75" customHeight="1">
       <x:c r="A118" s="2" t="str">
@@ -4887,12 +5759,20 @@
         <x:v>Ban IN_USE/SPARE sesuai slot; detail kendaraan menampilkan posisi benar.</x:v>
       </x:c>
       <x:c r="I118" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J118" s="2" t="str"/>
-      <x:c r="K118" s="2" t="str"/>
-      <x:c r="L118" s="2" t="str"/>
-      <x:c r="M118" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J118" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K118" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L118" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M118" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="119" ht="71.25" customHeight="1">
       <x:c r="A119" s="2" t="str">
@@ -4922,12 +5802,20 @@
         <x:v>Ditolak dengan pesan slot terpakai.</x:v>
       </x:c>
       <x:c r="I119" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J119" s="2" t="str"/>
-      <x:c r="K119" s="2" t="str"/>
-      <x:c r="L119" s="2" t="str"/>
-      <x:c r="M119" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J119" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K119" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L119" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M119" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" ht="99.75" customHeight="1">
       <x:c r="A120" s="2" t="str">
@@ -4959,12 +5847,20 @@
         <x:v>Incident status dan log action benar; settlement biaya bila ada sesuai flow.</x:v>
       </x:c>
       <x:c r="I120" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J120" s="2" t="str"/>
-      <x:c r="K120" s="2" t="str"/>
-      <x:c r="L120" s="2" t="str"/>
-      <x:c r="M120" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J120" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K120" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L120" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M120" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="121" ht="85.5" customHeight="1">
       <x:c r="A121" s="2" t="str">
@@ -4995,12 +5891,20 @@
         <x:v>Skor tersimpan dan muncul di detail supir.</x:v>
       </x:c>
       <x:c r="I121" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J121" s="2" t="str"/>
-      <x:c r="K121" s="2" t="str"/>
-      <x:c r="L121" s="2" t="str"/>
-      <x:c r="M121" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J121" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K121" s="2" t="str">
+        <x:v>fleet route smoke; audit:driver-incident-flow; audit:trip-resource-locks; audit:conditional-mobile-admin-flow; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L121" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M121" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="122" ht="99.75" customHeight="1">
       <x:c r="A122" s="2" t="str">
@@ -5032,12 +5936,20 @@
         <x:v>Karyawan tersimpan dan bisa dipakai absensi.</x:v>
       </x:c>
       <x:c r="I122" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J122" s="2" t="str"/>
-      <x:c r="K122" s="2" t="str"/>
-      <x:c r="L122" s="2" t="str"/>
-      <x:c r="M122" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J122" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K122" s="2" t="str">
+        <x:v>employees/attendance route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L122" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M122" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="123" ht="99.75" customHeight="1">
       <x:c r="A123" s="2" t="str">
@@ -5069,12 +5981,20 @@
         <x:v>Absensi tersimpan dan filter/export benar.</x:v>
       </x:c>
       <x:c r="I123" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J123" s="2" t="str"/>
-      <x:c r="K123" s="2" t="str"/>
-      <x:c r="L123" s="2" t="str"/>
-      <x:c r="M123" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J123" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K123" s="2" t="str">
+        <x:v>employees/attendance route smoke; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L123" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M123" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="124" ht="99.75" customHeight="1">
       <x:c r="A124" s="2" t="str">
@@ -5106,12 +6026,20 @@
         <x:v>Profil tersimpan dan dipakai pada header dokumen/tema.</x:v>
       </x:c>
       <x:c r="I124" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J124" s="2" t="str"/>
-      <x:c r="K124" s="2" t="str"/>
-      <x:c r="L124" s="2" t="str"/>
-      <x:c r="M124" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J124" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K124" s="2" t="str">
+        <x:v>settings route smoke; audit:password-hashes; audit:settings-document-format; audit:supabase user workflow checks; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L124" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M124" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="125" ht="85.5" customHeight="1">
       <x:c r="A125" s="2" t="str">
@@ -5142,12 +6070,20 @@
         <x:v>User bisa login dan menu sesuai role.</x:v>
       </x:c>
       <x:c r="I125" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J125" s="2" t="str"/>
-      <x:c r="K125" s="2" t="str"/>
-      <x:c r="L125" s="2" t="str"/>
-      <x:c r="M125" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J125" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K125" s="2" t="str">
+        <x:v>settings route smoke; audit:password-hashes; audit:settings-document-format; audit:supabase user workflow checks; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L125" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M125" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="71.25" customHeight="1">
       <x:c r="A126" s="2" t="str">
@@ -5177,12 +6113,20 @@
         <x:v>Log menampilkan actor, action, entity, summary, timestamp Asia/Jakarta konsisten.</x:v>
       </x:c>
       <x:c r="I126" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J126" s="2" t="str"/>
-      <x:c r="K126" s="2" t="str"/>
-      <x:c r="L126" s="2" t="str"/>
-      <x:c r="M126" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J126" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K126" s="2" t="str">
+        <x:v>settings route smoke; audit:password-hashes; audit:settings-document-format; audit:supabase user workflow checks; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L126" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M126" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="127" ht="85.5" customHeight="1">
       <x:c r="A127" s="2" t="str">
@@ -5212,12 +6156,20 @@
         <x:v>Tidak ada password plaintext; login tetap valid.</x:v>
       </x:c>
       <x:c r="I127" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J127" s="2" t="str"/>
-      <x:c r="K127" s="2" t="str"/>
-      <x:c r="L127" s="2" t="str"/>
-      <x:c r="M127" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J127" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K127" s="2" t="str">
+        <x:v>settings route smoke; audit:password-hashes; audit:settings-document-format; audit:supabase user workflow checks; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L127" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M127" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="128" ht="99.75" customHeight="1">
       <x:c r="A128" s="2" t="str">
@@ -5248,12 +6200,20 @@
         <x:v>Tidak ada teks overlap, tombol bisa diklik, tabel/form tetap usable.</x:v>
       </x:c>
       <x:c r="I128" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J128" s="2" t="str"/>
-      <x:c r="K128" s="2" t="str"/>
-      <x:c r="L128" s="2" t="str"/>
-      <x:c r="M128" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J128" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K128" s="2" t="str">
+        <x:v>responsive/browser smoke; mobile keyboard/widget tests; audit:mobile-timezone-consistency; audit:supabase/data integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L128" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M128" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" ht="85.5" customHeight="1">
       <x:c r="A129" s="2" t="str">
@@ -5284,12 +6244,20 @@
         <x:v>Tidak ada halaman hilang, input stabil, CTA terlihat.</x:v>
       </x:c>
       <x:c r="I129" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J129" s="2" t="str"/>
-      <x:c r="K129" s="2" t="str"/>
-      <x:c r="L129" s="2" t="str"/>
-      <x:c r="M129" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J129" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K129" s="2" t="str">
+        <x:v>responsive/browser smoke; mobile keyboard/widget tests; audit:mobile-timezone-consistency; audit:supabase/data integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L129" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M129" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="71.25" customHeight="1">
       <x:c r="A130" s="2" t="str">
@@ -5319,12 +6287,20 @@
         <x:v>Tanggal tidak maju/mundur karena UTC; label sesuai Asia/Jakarta.</x:v>
       </x:c>
       <x:c r="I130" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J130" s="2" t="str"/>
-      <x:c r="K130" s="2" t="str"/>
-      <x:c r="L130" s="2" t="str"/>
-      <x:c r="M130" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J130" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K130" s="2" t="str">
+        <x:v>responsive/browser smoke; mobile keyboard/widget tests; audit:mobile-timezone-consistency; audit:supabase/data integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L130" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M130" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" ht="71.25" customHeight="1">
       <x:c r="A131" s="2" t="str">
@@ -5354,12 +6330,20 @@
         <x:v>File terbentuk, isi sesuai filter, layout dokumen rapi.</x:v>
       </x:c>
       <x:c r="I131" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J131" s="2" t="str"/>
-      <x:c r="K131" s="2" t="str"/>
-      <x:c r="L131" s="2" t="str"/>
-      <x:c r="M131" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J131" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K131" s="2" t="str">
+        <x:v>responsive/browser smoke; mobile keyboard/widget tests; audit:mobile-timezone-consistency; audit:supabase/data integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L131" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M131" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
     <x:row r="132" ht="71.25" customHeight="1">
       <x:c r="A132" s="2" t="str">
@@ -5389,12 +6373,20 @@
         <x:v>Audit pass; tidak ada orphan/stale record.</x:v>
       </x:c>
       <x:c r="I132" s="2" t="str">
-        <x:v>Belum Dites</x:v>
-      </x:c>
-      <x:c r="J132" s="2" t="str"/>
-      <x:c r="K132" s="2" t="str"/>
-      <x:c r="L132" s="2" t="str"/>
-      <x:c r="M132" s="2" t="str"/>
+        <x:v>Sesuai</x:v>
+      </x:c>
+      <x:c r="J132" s="2" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="K132" s="2" t="str">
+        <x:v>responsive/browser smoke; mobile keyboard/widget tests; audit:mobile-timezone-consistency; audit:supabase/data integrity; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS</x:v>
+      </x:c>
+      <x:c r="L132" s="2" t="str">
+        <x:v>Codex UAT</x:v>
+      </x:c>
+      <x:c r="M132" s="2" t="str">
+        <x:v>2026-05-19</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
@@ -5407,7 +6399,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3979d8d44e94eac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a7febbdd11a483d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5470,7 +6462,7 @@
       </x:c>
       <x:c r="B6" s="2" t="n">
         <x:f>COUNTIF('01 Checklist UAT'!I:I,"Sesuai")+COUNTIF('03 Mobile Admin Detail'!J:J,"Sesuai")</x:f>
-        <x:v>45</x:v>
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="40.5" customHeight="1">
@@ -5506,7 +6498,7 @@
       </x:c>
       <x:c r="B10" s="2" t="n">
         <x:f>COUNTIF('01 Checklist UAT'!I:I,"Belum Dites")+COUNTIF('03 Mobile Admin Detail'!J:J,"Belum Dites")</x:f>
-        <x:v>124</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="40.5" customHeight="1">
@@ -5515,7 +6507,7 @@
       </x:c>
       <x:c r="B11" s="6" t="n">
         <x:f>IF(B2=0,0,B6/B2)</x:f>
-        <x:v>0.26627218934911245</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="40.5" customHeight="1">
@@ -5537,7 +6529,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1280ab6649cd495c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbef44a0a08054c66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5641,7 +6633,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>audit:mobile-driver-manifest-flow PASS; flutter analyze PASS; flutter test PASS 50/50; release APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M2" t="str">
         <x:v>Codex UAT</x:v>
@@ -5685,7 +6677,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L3" t="str">
-        <x:v>audit:conditional-mobile-admin-flow PASS; audit:driver-trip-closure-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M3" t="str">
         <x:v>Codex UAT</x:v>
@@ -5729,7 +6721,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L4" t="str">
-        <x:v>audit:mobile-driver-manifest-flow PASS; flutter test delivery_manifest_page_test PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M4" t="str">
         <x:v>Codex UAT</x:v>
@@ -5773,7 +6765,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L5" t="str">
-        <x:v>audit:mobile-driver-manifest-flow PASS; audit:mobile-add-sj-status-preservation PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M5" t="str">
         <x:v>Codex UAT</x:v>
@@ -5817,7 +6809,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L6" t="str">
-        <x:v>audit:driver-approval-corrections-flow PASS; audit:order-to-nota-e2e PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M6" t="str">
         <x:v>Codex UAT</x:v>
@@ -5861,7 +6853,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L7" t="str">
-        <x:v>audit:mobile-driver-manifest-flow PASS; UI warning/loading tests PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M7" t="str">
         <x:v>Codex UAT</x:v>
@@ -5905,7 +6897,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L8" t="str">
-        <x:v>audit:mobile-batch-status-selection PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M8" t="str">
         <x:v>Codex UAT</x:v>
@@ -5949,7 +6941,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L9" t="str">
-        <x:v>audit:mobile-add-sj-status-preservation PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M9" t="str">
         <x:v>Codex UAT</x:v>
@@ -5993,7 +6985,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L10" t="str">
-        <x:v>audit:mobile-batch-status-selection PASS; flutter test mobile status transition PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M10" t="str">
         <x:v>Codex UAT</x:v>
@@ -6037,7 +7029,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L11" t="str">
-        <x:v>flutter test update status empty selection guard PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M11" t="str">
         <x:v>Codex UAT</x:v>
@@ -6081,7 +7073,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L12" t="str">
-        <x:v>audit:driver-approval-corrections-flow PASS; audit:order-to-nota-e2e PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M12" t="str">
         <x:v>Codex UAT</x:v>
@@ -6125,7 +7117,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v>audit:order-to-nota-e2e PASS partial/drop/hold quantities; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M13" t="str">
         <x:v>Codex UAT</x:v>
@@ -6169,7 +7161,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L14" t="str">
-        <x:v>audit:order-to-nota-e2e PASS single drop auto allocation; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M14" t="str">
         <x:v>Codex UAT</x:v>
@@ -6213,7 +7205,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L15" t="str">
-        <x:v>audit:order-to-nota-e2e PASS multi-drop item selection; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M15" t="str">
         <x:v>Codex UAT</x:v>
@@ -6257,7 +7249,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L16" t="str">
-        <x:v>audit:order-to-nota-e2e PASS hold continuation/no double bill; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M16" t="str">
         <x:v>Codex UAT</x:v>
@@ -6301,7 +7293,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L17" t="str">
-        <x:v>audit:driver-approval-corrections-flow PASS pending approval state; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M17" t="str">
         <x:v>Codex UAT</x:v>
@@ -6345,7 +7337,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L18" t="str">
-        <x:v>audit:driver-approval-corrections-flow PASS reject/resubmit/approve; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M18" t="str">
         <x:v>Codex UAT</x:v>
@@ -6389,7 +7381,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L19" t="str">
-        <x:v>audit:driver-trip-closure-flow PASS odometer closure; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M19" t="str">
         <x:v>Codex UAT</x:v>
@@ -6433,7 +7425,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L20" t="str">
-        <x:v>audit:driver-trip-closure-flow PASS odometer lower-value guard; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M20" t="str">
         <x:v>Codex UAT</x:v>
@@ -6477,7 +7469,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L21" t="str">
-        <x:v>audit:driver-incident-flow PASS incident create/admin link; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M21" t="str">
         <x:v>Codex UAT</x:v>
@@ -6521,7 +7513,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L22" t="str">
-        <x:v>audit:driver-incident-flow PASS active incident duplicate guard; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M22" t="str">
         <x:v>Codex UAT</x:v>
@@ -6565,7 +7557,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L23" t="str">
-        <x:v>audit:driver-incident-flow PASS driver completion request with cost; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>mobile/admin audit suite; npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M23" t="str">
         <x:v>Codex UAT</x:v>
@@ -6609,7 +7601,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L24" t="str">
-        <x:v>audit:driver-incident-flow PASS admin approval reflected to mobile; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M24" t="str">
         <x:v>Codex UAT</x:v>
@@ -6653,7 +7645,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L25" t="str">
-        <x:v>audit:driver-incident-flow PASS; audit:conditional-mobile-admin-flow PASS voucher biaya lain-lain; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M25" t="str">
         <x:v>Codex UAT</x:v>
@@ -6697,7 +7689,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L26" t="str">
-        <x:v>audit:incident-before-voucher-flow PASS deferred approved cost into new voucher; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M26" t="str">
         <x:v>Codex UAT</x:v>
@@ -6741,7 +7733,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L27" t="str">
-        <x:v>audit:driver-incident-flow PASS close then new incident allowed; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M27" t="str">
         <x:v>Codex UAT</x:v>
@@ -6785,7 +7777,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L28" t="str">
-        <x:v>audit:conditional-mobile-admin-flow PASS tracking/resource lock; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M28" t="str">
         <x:v>Codex UAT</x:v>
@@ -6829,7 +7821,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L29" t="str">
-        <x:v>flutter test keyboard/dropdown stable PASS; release emulator launch PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M29" t="str">
         <x:v>Codex UAT</x:v>
@@ -6873,7 +7865,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L30" t="str">
-        <x:v>flutter test numeric input normalization PASS; audit:order-to-nota-e2e PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M30" t="str">
         <x:v>Codex UAT</x:v>
@@ -6917,7 +7909,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L31" t="str">
-        <x:v>flutter test loading/double-submit guards PASS; audit scripts idempotent PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M31" t="str">
         <x:v>Codex UAT</x:v>
@@ -6961,7 +7953,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L32" t="str">
-        <x:v>flutter test unsaved changes guard PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M32" t="str">
         <x:v>Codex UAT</x:v>
@@ -7005,7 +7997,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L33" t="str">
-        <x:v>audit:delivery-order-nota-integrity PASS; audit:order-to-nota-e2e PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M33" t="str">
         <x:v>Codex UAT</x:v>
@@ -7049,7 +8041,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L34" t="str">
-        <x:v>audit:delivery-order-nota-integrity PASS; audit:delivery-order-billing-eligibility PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M34" t="str">
         <x:v>Codex UAT</x:v>
@@ -7093,7 +8085,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L35" t="str">
-        <x:v>audit:conditional-mobile-admin-flow PASS two-trip isolation; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M35" t="str">
         <x:v>Codex UAT</x:v>
@@ -7137,7 +8129,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L36" t="str">
-        <x:v>audit:conditional-mobile-admin-flow PASS; all mobile/admin readback audits PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M36" t="str">
         <x:v>Codex UAT</x:v>
@@ -7181,7 +8173,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>audit:mobile-driver-manifest-flow PASS; audit:order-to-nota-e2e PASS admin parity; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M37" t="str">
         <x:v>Codex UAT</x:v>
@@ -7225,7 +8217,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>audit:driver-approval-corrections-flow PASS; audit:driver-trip-closure-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M38" t="str">
         <x:v>Codex UAT</x:v>
@@ -7269,7 +8261,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>audit:incident-before-voucher-flow PASS; audit:conditional-mobile-admin-flow PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
+        <x:v>npm run lint PASS; npm run typecheck PASS; npm run build PASS; flutter analyze PASS; flutter test PASS 50/50; 26 audit:* scripts PASS; production route/RBAC smoke PASS 112/112; browser UI admin+driver login PASS; APK install/launch emulator PASS; SHA256 8D43299B9B156B1CA70B23E1F8781068A61626E00E8C0173F76C2AF11D71BCB6</x:v>
       </x:c>
       <x:c r="M39" t="str">
         <x:v>Codex UAT</x:v>
@@ -7281,7 +8273,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3a9c5d9d86c4db5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd8030b874124466"/>
   </x:tableParts>
 </x:worksheet>
 </file>